--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
         <v>2.96</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,7 +981,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q3" t="n">
         <v>2.48</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q3" t="n">
         <v>2.48</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="G2" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="H2" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="I2" t="n">
         <v>6.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q2" t="n">
         <v>2.16</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -957,13 +957,13 @@
         <v>2.96</v>
       </c>
       <c r="H3" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="I3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J3" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="K3" t="n">
         <v>3.25</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH3"/>
+  <dimension ref="A1:BH4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 09:23:00</t>
+          <t>2026-03-24 11:28:59</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2.68</v>
       </c>
       <c r="G3" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="H3" t="n">
         <v>2.96</v>
@@ -1114,7 +1114,201 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 09:23:00</t>
+          <t>2026-03-24 11:28:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Deportivo Recoleta</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Rubio Nu</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:28:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH4"/>
+  <dimension ref="A1:BH5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="G2" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="H2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I2" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
         <v>3.45</v>
@@ -775,152 +775,152 @@
         <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P2" t="n">
         <v>1.67</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
@@ -1114,201 +1114,395 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Union Magdalena</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Real Santander</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>2026-03-24 13:35:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Deportivo Recoleta</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Rubio Nu</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="F5" t="n">
         <v>2.46</v>
       </c>
-      <c r="G4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="G5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H5" t="n">
         <v>2.96</v>
       </c>
-      <c r="I4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="I5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J5" t="n">
         <v>2.86</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K5" t="n">
         <v>3.95</v>
       </c>
-      <c r="L4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="L5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M5" t="n">
         <v>1.09</v>
       </c>
-      <c r="N4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="O4" t="n">
+      <c r="N5" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V5" t="n">
         <v>1.4</v>
       </c>
-      <c r="P4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X4" t="n">
+      <c r="W5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X5" t="n">
         <v>970</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Y5" t="n">
         <v>970</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="Z5" t="n">
         <v>24</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AA5" t="n">
         <v>70</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AB5" t="n">
         <v>970</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AC5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD5" t="n">
         <v>970</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AE5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF5" t="n">
         <v>970</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AG5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>48</v>
       </c>
-      <c r="AF4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK4" t="n">
+      <c r="AK5" t="n">
         <v>38</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AL5" t="n">
         <v>60</v>
       </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
         <v>38</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AO5" t="n">
         <v>55</v>
       </c>
-      <c r="AP4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AR4" t="n">
+      <c r="AP5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR5" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="AS5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA5" t="n">
         <v>4.7</v>
       </c>
-      <c r="AT4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW4" t="n">
+      <c r="BB5" t="n">
         <v>4.6</v>
       </c>
-      <c r="AX4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA4" t="n">
+      <c r="BC5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD5" t="n">
         <v>4.7</v>
       </c>
-      <c r="BB4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE4" t="n">
+      <c r="BE5" t="n">
         <v>4.9</v>
       </c>
-      <c r="BF4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>2026-03-24 11:28:59</t>
+      <c r="BF5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH5"/>
+  <dimension ref="A1:BH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,13 +760,13 @@
         <v>1.8</v>
       </c>
       <c r="G2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="H2" t="n">
         <v>5.3</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J2" t="n">
         <v>3.45</v>
@@ -778,19 +778,19 @@
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>1.55</v>
+        <v>2.82</v>
       </c>
       <c r="O2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P2" t="n">
         <v>1.67</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R2" t="n">
         <v>1.19</v>
@@ -799,22 +799,22 @@
         <v>3.75</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="V2" t="n">
         <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z2" t="n">
         <v>1000</v>
@@ -823,10 +823,10 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD2" t="n">
         <v>1000</v>
@@ -835,10 +835,10 @@
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH2" t="n">
         <v>1000</v>
@@ -865,52 +865,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
         <v>1.02</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1178,7 +1178,7 @@
         <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,201 +1308,589 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Internacional de Palmira</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Tigres FC Zipaquira</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K5" t="n">
+        <v>950</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>2026-03-24 15:41:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Independiente Yumbo</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Boyaca Patriotas</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2026-03-24 15:41:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Deportivo Recoleta</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Rubio Nu</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F7" t="n">
         <v>2.46</v>
       </c>
-      <c r="G5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="G7" t="n">
         <v>2.96</v>
       </c>
-      <c r="I5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="H7" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J7" t="n">
         <v>2.86</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K7" t="n">
         <v>3.95</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L7" t="n">
         <v>1.42</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M7" t="n">
         <v>1.09</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N7" t="n">
         <v>2.98</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O7" t="n">
         <v>1.41</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P7" t="n">
         <v>1.67</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q7" t="n">
         <v>2.16</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R7" t="n">
         <v>1.25</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S7" t="n">
         <v>3.85</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T7" t="n">
         <v>1.86</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U7" t="n">
         <v>1.92</v>
       </c>
-      <c r="V5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W5" t="n">
+      <c r="V7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.53</v>
       </c>
-      <c r="X5" t="n">
+      <c r="X7" t="n">
         <v>970</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Y7" t="n">
         <v>970</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="Z7" t="n">
         <v>24</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AA7" t="n">
         <v>70</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AB7" t="n">
         <v>970</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AC7" t="n">
         <v>8.4</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AD7" t="n">
         <v>970</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AE7" t="n">
         <v>48</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AF7" t="n">
         <v>970</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AG7" t="n">
         <v>970</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AH7" t="n">
         <v>22</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AI7" t="n">
         <v>65</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AJ7" t="n">
         <v>48</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AK7" t="n">
         <v>38</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AL7" t="n">
         <v>60</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AM7" t="n">
         <v>1000</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AN7" t="n">
         <v>38</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AO7" t="n">
         <v>55</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AP7" t="n">
         <v>8.4</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AQ7" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AR7" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT5" t="n">
+      <c r="AS7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT7" t="n">
         <v>7.2</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AU7" t="n">
         <v>5.8</v>
       </c>
-      <c r="AV5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW5" t="n">
+      <c r="AV7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW7" t="n">
         <v>4.6</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="AX7" t="n">
         <v>4</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="AY7" t="n">
         <v>9.4</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA5" t="n">
+      <c r="AZ7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA7" t="n">
         <v>4.7</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BB7" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE5" t="n">
+      <c r="BC7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE7" t="n">
         <v>4.9</v>
       </c>
-      <c r="BF5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>2026-03-24 13:35:31</t>
+      <c r="BF7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -757,43 +757,43 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="H2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I2" t="n">
         <v>5.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="O2" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="P2" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="S2" t="n">
         <v>3.75</v>
@@ -802,13 +802,13 @@
         <v>1.89</v>
       </c>
       <c r="U2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V2" t="n">
         <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -838,7 +838,7 @@
         <v>15</v>
       </c>
       <c r="AG2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH2" t="n">
         <v>1000</v>
@@ -865,40 +865,40 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.91</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.91</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AV2" t="n">
         <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.91</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY2" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14.5</v>
+        <v>1.91</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.91</v>
       </c>
       <c r="BB2" t="n">
         <v>12.5</v>
@@ -907,20 +907,20 @@
         <v>14</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.91</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.91</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
@@ -969,16 +969,16 @@
         <v>3.25</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="P3" t="n">
         <v>1.55</v>
@@ -987,134 +987,134 @@
         <v>2.56</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
@@ -1730,22 +1730,22 @@
         <v>2.46</v>
       </c>
       <c r="G7" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="H7" t="n">
         <v>2.96</v>
       </c>
       <c r="I7" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J7" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K7" t="n">
         <v>3.95</v>
       </c>
       <c r="L7" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
@@ -1775,7 +1775,7 @@
         <v>1.92</v>
       </c>
       <c r="V7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
         <v>1.53</v>
@@ -1796,7 +1796,7 @@
         <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AD7" t="n">
         <v>970</v>
@@ -1853,7 +1853,7 @@
         <v>5.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.85</v>
+        <v>10.5</v>
       </c>
       <c r="AW7" t="n">
         <v>4.6</v>
@@ -1862,7 +1862,7 @@
         <v>4</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.4</v>
+        <v>3.8</v>
       </c>
       <c r="AZ7" t="n">
         <v>4.1</v>
@@ -1874,23 +1874,23 @@
         <v>4.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE7" t="n">
         <v>4.9</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -793,7 +793,7 @@
         <v>2.1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S2" t="n">
         <v>3.75</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2.68</v>
       </c>
       <c r="G3" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="H3" t="n">
         <v>2.96</v>
@@ -978,7 +978,7 @@
         <v>1.56</v>
       </c>
       <c r="O3" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P3" t="n">
         <v>1.55</v>
@@ -990,7 +990,7 @@
         <v>1.16</v>
       </c>
       <c r="S3" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1002,7 +1002,7 @@
         <v>1.45</v>
       </c>
       <c r="W3" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1062,13 +1062,13 @@
         <v>7.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="AT3" t="n">
         <v>6.6</v>
@@ -1077,13 +1077,13 @@
         <v>5.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="AX3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
@@ -1092,29 +1092,29 @@
         <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>1.58</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.83</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.51</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>1.91</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -1730,13 +1730,13 @@
         <v>2.46</v>
       </c>
       <c r="G7" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="H7" t="n">
         <v>2.96</v>
       </c>
       <c r="I7" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="J7" t="n">
         <v>2.84</v>
@@ -1745,7 +1745,7 @@
         <v>3.95</v>
       </c>
       <c r="L7" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
@@ -1775,10 +1775,10 @@
         <v>1.92</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -1841,10 +1841,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT7" t="n">
         <v>7.2</v>
@@ -1853,34 +1853,34 @@
         <v>5.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>10.5</v>
+        <v>3.95</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX7" t="n">
         <v>4</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB7" t="n">
         <v>4.7</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.6</v>
       </c>
       <c r="BC7" t="n">
         <v>4.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="BF7" t="n">
         <v>4.5</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -760,16 +760,16 @@
         <v>1.74</v>
       </c>
       <c r="G2" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="H2" t="n">
         <v>5.2</v>
       </c>
       <c r="I2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
         <v>4.1</v>
@@ -808,7 +808,7 @@
         <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -978,13 +978,13 @@
         <v>1.56</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="P3" t="n">
         <v>1.55</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="R3" t="n">
         <v>1.16</v>
@@ -1089,7 +1089,7 @@
         <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA3" t="n">
         <v>2.06</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="G4" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="H4" t="n">
         <v>7.2</v>
@@ -1160,7 +1160,7 @@
         <v>4.2</v>
       </c>
       <c r="K4" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1169,22 +1169,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>1.83</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="R4" t="n">
         <v>1.13</v>
       </c>
       <c r="S4" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1196,7 +1196,7 @@
         <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G5" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="H5" t="n">
         <v>5.1</v>
       </c>
       <c r="I5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
         <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1366,19 +1366,19 @@
         <v>1.51</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="P5" t="n">
         <v>1.51</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="R5" t="n">
         <v>1.13</v>
       </c>
       <c r="S5" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1387,10 +1387,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W5" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1447,52 +1447,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="G6" t="n">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="H6" t="n">
         <v>2.74</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="J6" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="P6" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -1730,13 +1730,13 @@
         <v>2.46</v>
       </c>
       <c r="G7" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="H7" t="n">
         <v>2.96</v>
       </c>
       <c r="I7" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="J7" t="n">
         <v>2.84</v>
@@ -1745,7 +1745,7 @@
         <v>3.95</v>
       </c>
       <c r="L7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
@@ -1775,7 +1775,7 @@
         <v>1.92</v>
       </c>
       <c r="V7" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
         <v>1.5</v>
@@ -1841,10 +1841,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT7" t="n">
         <v>7.2</v>
@@ -1853,44 +1853,44 @@
         <v>5.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AX7" t="n">
         <v>4</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.85</v>
+        <v>9.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BB7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD7" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BE7" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH7"/>
+  <dimension ref="A1:BH9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H2" t="n">
         <v>5.2</v>
@@ -769,7 +769,7 @@
         <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
         <v>4.1</v>
@@ -808,7 +808,7 @@
         <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
         <v>7</v>
       </c>
       <c r="AR3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS3" t="n">
         <v>2.06</v>
@@ -1077,19 +1077,19 @@
         <v>5.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW3" t="n">
         <v>2.06</v>
       </c>
       <c r="AX3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA3" t="n">
         <v>2.06</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="G4" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="H4" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="K4" t="n">
-        <v>9.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1169,22 +1169,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>3.45</v>
       </c>
       <c r="O4" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="R4" t="n">
         <v>1.13</v>
       </c>
       <c r="S4" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1193,10 +1193,10 @@
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>1.52</v>
       </c>
       <c r="G5" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H5" t="n">
         <v>5.1</v>
@@ -1363,10 +1363,10 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.51</v>
+        <v>2.86</v>
       </c>
       <c r="O5" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="P5" t="n">
         <v>1.51</v>
@@ -1390,7 +1390,7 @@
         <v>1.11</v>
       </c>
       <c r="W5" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -1539,46 +1539,46 @@
         <v>2.44</v>
       </c>
       <c r="H6" t="n">
-        <v>2.74</v>
+        <v>3.45</v>
       </c>
       <c r="I6" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>2.46</v>
+        <v>2.78</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>1.54</v>
+        <v>2.38</v>
       </c>
       <c r="O6" t="n">
-        <v>1.09</v>
+        <v>1.53</v>
       </c>
       <c r="P6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q6" t="n">
         <v>2.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="S6" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="V6" t="n">
         <v>1.3</v>
@@ -1599,10 +1599,10 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1644,7 +1644,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
         <v>1.03</v>
@@ -1653,10 +1653,10 @@
         <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
         <v>1.03</v>
@@ -1665,10 +1665,10 @@
         <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
         <v>1.03</v>
@@ -1689,14 +1689,14 @@
         <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="G7" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H7" t="n">
         <v>2.88</v>
       </c>
-      <c r="H7" t="n">
-        <v>2.96</v>
-      </c>
       <c r="I7" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="J7" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
         <v>1.43</v>
@@ -1760,7 +1760,7 @@
         <v>1.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R7" t="n">
         <v>1.25</v>
@@ -1772,13 +1772,13 @@
         <v>1.86</v>
       </c>
       <c r="U7" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V7" t="n">
         <v>1.41</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -1790,13 +1790,13 @@
         <v>24</v>
       </c>
       <c r="AA7" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB7" t="n">
         <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
         <v>970</v>
@@ -1820,7 +1820,7 @@
         <v>48</v>
       </c>
       <c r="AK7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL7" t="n">
         <v>60</v>
@@ -1829,7 +1829,7 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO7" t="n">
         <v>55</v>
@@ -1838,59 +1838,447 @@
         <v>8.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AT7" t="n">
         <v>7.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.8</v>
+        <v>3.35</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AX7" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AY7" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Lanus</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>220</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>290</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>240</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2026-03-25 00:04:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Quindio</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Orsomarso</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G2" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="H2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I2" t="n">
         <v>6</v>
@@ -781,40 +781,40 @@
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="P2" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q2" t="n">
         <v>2.1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="V2" t="n">
         <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y2" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
         <v>1000</v>
@@ -823,10 +823,10 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
         <v>1000</v>
@@ -835,10 +835,10 @@
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="AH2" t="n">
         <v>1000</v>
@@ -853,13 +853,13 @@
         <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
@@ -868,59 +868,59 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.91</v>
+        <v>7.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.91</v>
+        <v>4.6</v>
       </c>
       <c r="AT2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX2" t="n">
         <v>4.8</v>
       </c>
-      <c r="AU2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AY2" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.91</v>
+        <v>6.8</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.91</v>
+        <v>8.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>12.5</v>
+        <v>6.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>14</v>
+        <v>6.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.91</v>
+        <v>4.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.91</v>
+        <v>4.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.91</v>
+        <v>6</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.91</v>
+        <v>8.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         <v>2.96</v>
       </c>
       <c r="I3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J3" t="n">
         <v>2.94</v>
@@ -972,31 +972,31 @@
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P3" t="n">
         <v>1.56</v>
       </c>
-      <c r="O3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.55</v>
-      </c>
       <c r="Q3" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="R3" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="S3" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="V3" t="n">
         <v>1.45</v>
@@ -1005,116 +1005,116 @@
         <v>1.51</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AW3" t="n">
-        <v>2.06</v>
+        <v>5.1</v>
       </c>
       <c r="AX3" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16</v>
+        <v>4.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.06</v>
+        <v>50</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.06</v>
+        <v>5</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.06</v>
+        <v>34</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.06</v>
+        <v>5.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.06</v>
+        <v>5.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.06</v>
+        <v>5.1</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.06</v>
+        <v>5.1</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -1154,10 +1154,10 @@
         <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="K4" t="n">
         <v>5.5</v>
@@ -1166,7 +1166,7 @@
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
         <v>3.45</v>
@@ -1181,19 +1181,19 @@
         <v>1.94</v>
       </c>
       <c r="R4" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
-        <v>1.96</v>
+        <v>3.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="V4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W4" t="n">
         <v>3.3</v>
@@ -1202,7 +1202,7 @@
         <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Z4" t="n">
         <v>1000</v>
@@ -1211,10 +1211,10 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AD4" t="n">
         <v>1000</v>
@@ -1223,10 +1223,10 @@
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH4" t="n">
         <v>1000</v>
@@ -1235,10 +1235,10 @@
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL4" t="n">
         <v>1000</v>
@@ -1256,7 +1256,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AR4" t="n">
         <v>1.03</v>
@@ -1265,10 +1265,10 @@
         <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
         <v>1.03</v>
@@ -1277,10 +1277,10 @@
         <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AZ4" t="n">
         <v>1.03</v>
@@ -1289,10 +1289,10 @@
         <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BD4" t="n">
         <v>1.03</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G6" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="H6" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
         <v>3.8</v>
@@ -1584,7 +1584,7 @@
         <v>1.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="G7" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="I7" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.43</v>
@@ -1751,7 +1751,7 @@
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O7" t="n">
         <v>1.41</v>
@@ -1775,10 +1775,10 @@
         <v>1.94</v>
       </c>
       <c r="V7" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -1787,22 +1787,22 @@
         <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA7" t="n">
         <v>65</v>
       </c>
       <c r="AB7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC7" t="n">
         <v>970</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
         <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF7" t="n">
         <v>970</v>
@@ -1832,7 +1832,7 @@
         <v>34</v>
       </c>
       <c r="AO7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP7" t="n">
         <v>8.4</v>
@@ -1841,56 +1841,56 @@
         <v>8</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.1</v>
+        <v>2.62</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AW7" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.3</v>
+        <v>12.5</v>
       </c>
       <c r="AY7" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.55</v>
+        <v>2.62</v>
       </c>
       <c r="BB7" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.1</v>
+        <v>3.35</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.3</v>
+        <v>2.48</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -1981,13 +1981,13 @@
         <v>14</v>
       </c>
       <c r="Z8" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AA8" t="n">
         <v>220</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC8" t="n">
         <v>8.199999999999999</v>
@@ -2011,10 +2011,10 @@
         <v>160</v>
       </c>
       <c r="AJ8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AL8" t="n">
         <v>70</v>
@@ -2035,10 +2035,10 @@
         <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>32</v>
+        <v>7.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT8" t="n">
         <v>5.5</v>
@@ -2050,19 +2050,19 @@
         <v>18</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX8" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY8" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.2</v>
+        <v>23</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB8" t="n">
         <v>17</v>
@@ -2071,20 +2071,20 @@
         <v>20</v>
       </c>
       <c r="BD8" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF8" t="n">
         <v>17.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -757,40 +757,40 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="G2" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H2" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O2" t="n">
         <v>1.39</v>
       </c>
       <c r="P2" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R2" t="n">
         <v>1.28</v>
@@ -799,19 +799,19 @@
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U2" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X2" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
         <v>1000</v>
@@ -823,7 +823,7 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC2" t="n">
         <v>1000</v>
@@ -853,13 +853,13 @@
         <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
@@ -868,59 +868,59 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.6</v>
+        <v>10</v>
       </c>
       <c r="AT2" t="n">
         <v>6.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AY2" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BA2" t="n">
         <v>6.8</v>
       </c>
-      <c r="BA2" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BB2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF2" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>6</v>
-      </c>
       <c r="BG2" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G3" t="n">
         <v>2.96</v>
@@ -963,7 +963,7 @@
         <v>3.25</v>
       </c>
       <c r="J3" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K3" t="n">
         <v>3.25</v>
@@ -975,10 +975,10 @@
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O3" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P3" t="n">
         <v>1.56</v>
@@ -990,10 +990,10 @@
         <v>1.2</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U3" t="n">
         <v>1.83</v>
@@ -1014,7 +1014,7 @@
         <v>23</v>
       </c>
       <c r="AA3" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
         <v>9.800000000000001</v>
@@ -1044,10 +1044,10 @@
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1065,10 +1065,10 @@
         <v>8</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT3" t="n">
         <v>7.6</v>
@@ -1080,7 +1080,7 @@
         <v>12</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX3" t="n">
         <v>15</v>
@@ -1089,32 +1089,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>50</v>
+        <v>5.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BC3" t="n">
-        <v>34</v>
+        <v>5.2</v>
       </c>
       <c r="BD3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF3" t="n">
         <v>5.2</v>
       </c>
-      <c r="BE3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BG3" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -1154,22 +1154,22 @@
         <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K4" t="n">
         <v>5.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -1178,31 +1178,31 @@
         <v>1.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R4" t="n">
         <v>1.32</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V4" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W4" t="n">
         <v>3.3</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y4" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="Z4" t="n">
         <v>1000</v>
@@ -1211,52 +1211,52 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AC4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AG4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>1.03</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>18.5</v>
       </c>
       <c r="AR4" t="n">
         <v>1.03</v>
@@ -1265,10 +1265,10 @@
         <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
         <v>1.03</v>
@@ -1277,10 +1277,10 @@
         <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
         <v>1.03</v>
@@ -1289,10 +1289,10 @@
         <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
         <v>1.03</v>
@@ -1301,14 +1301,14 @@
         <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -1339,100 +1339,100 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="G5" t="n">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="H5" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J5" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="O5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P5" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="R5" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>2.14</v>
+        <v>4.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="V5" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W5" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
         <v>1000</v>
@@ -1441,16 +1441,16 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AR5" t="n">
         <v>1.03</v>
@@ -1459,10 +1459,10 @@
         <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV5" t="n">
         <v>1.03</v>
@@ -1471,10 +1471,10 @@
         <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ5" t="n">
         <v>1.03</v>
@@ -1483,10 +1483,10 @@
         <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BD5" t="n">
         <v>1.03</v>
@@ -1495,14 +1495,14 @@
         <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -1536,55 +1536,55 @@
         <v>2.14</v>
       </c>
       <c r="G6" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P6" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="Q6" t="n">
         <v>2.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S6" t="n">
         <v>4.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="V6" t="n">
         <v>1.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1599,7 +1599,7 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC6" t="n">
         <v>1000</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>2.14</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>2.12</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>2.02</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>2.62</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>2.1</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>1.89</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>2.14</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>1.99</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>2.1</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>2.04</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>2.04</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>2.08</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>2.12</v>
       </c>
       <c r="BF6" t="n">
-        <v>25</v>
+        <v>2.04</v>
       </c>
       <c r="BG6" t="n">
-        <v>70</v>
+        <v>2.12</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="G7" t="n">
         <v>3</v>
@@ -1736,19 +1736,19 @@
         <v>2.84</v>
       </c>
       <c r="I7" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
         <v>1.43</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
         <v>2.96</v>
@@ -1760,13 +1760,13 @@
         <v>1.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R7" t="n">
         <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="T7" t="n">
         <v>1.86</v>
@@ -1775,7 +1775,7 @@
         <v>1.94</v>
       </c>
       <c r="V7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
         <v>1.5</v>
@@ -1787,7 +1787,7 @@
         <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
         <v>65</v>
@@ -1829,7 +1829,7 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AO7" t="n">
         <v>50</v>
@@ -1841,56 +1841,56 @@
         <v>8</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.62</v>
+        <v>2.22</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="AX7" t="n">
         <v>12.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.4</v>
+        <v>4.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BA7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG7" t="n">
         <v>2.62</v>
       </c>
-      <c r="BB7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -1924,13 +1924,13 @@
         <v>1.88</v>
       </c>
       <c r="G8" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
         <v>3.15</v>
@@ -1945,13 +1945,13 @@
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O8" t="n">
         <v>1.55</v>
       </c>
       <c r="P8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q8" t="n">
         <v>2.64</v>
@@ -1969,10 +1969,10 @@
         <v>1.66</v>
       </c>
       <c r="V8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
         <v>9.800000000000001</v>
@@ -1984,7 +1984,7 @@
         <v>44</v>
       </c>
       <c r="AA8" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AB8" t="n">
         <v>6.4</v>
@@ -1996,7 +1996,7 @@
         <v>25</v>
       </c>
       <c r="AE8" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF8" t="n">
         <v>10.5</v>
@@ -2005,10 +2005,10 @@
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI8" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ8" t="n">
         <v>23</v>
@@ -2020,25 +2020,25 @@
         <v>70</v>
       </c>
       <c r="AM8" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN8" t="n">
         <v>25</v>
       </c>
       <c r="AO8" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ8" t="n">
         <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT8" t="n">
         <v>5.5</v>
@@ -2062,7 +2062,7 @@
         <v>23</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB8" t="n">
         <v>17</v>
@@ -2074,17 +2074,17 @@
         <v>48</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF8" t="n">
         <v>17.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -2115,170 +2115,170 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="G9" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="H9" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="I9" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="X9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU9" t="n">
         <v>6.8</v>
       </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -757,40 +757,40 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="G2" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="H2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I2" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.39</v>
       </c>
       <c r="P2" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="R2" t="n">
         <v>1.28</v>
@@ -799,22 +799,22 @@
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="V2" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="W2" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z2" t="n">
         <v>1000</v>
@@ -823,34 +823,34 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL2" t="n">
         <v>1000</v>
@@ -859,68 +859,68 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY2" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX2" t="n">
+      <c r="AZ2" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA2" t="n">
         <v>5.3</v>
       </c>
-      <c r="AY2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BB2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BC2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BD2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2.7</v>
       </c>
       <c r="G3" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H3" t="n">
         <v>2.96</v>
@@ -963,10 +963,10 @@
         <v>3.25</v>
       </c>
       <c r="J3" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -975,34 +975,34 @@
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
         <v>1.51</v>
       </c>
       <c r="P3" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V3" t="n">
         <v>1.45</v>
       </c>
       <c r="W3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X3" t="n">
         <v>10.5</v>
@@ -1047,7 +1047,7 @@
         <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1059,7 +1059,7 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ3" t="n">
         <v>8</v>
@@ -1080,7 +1080,7 @@
         <v>12</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX3" t="n">
         <v>15</v>
@@ -1089,10 +1089,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.8</v>
+        <v>18.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB3" t="n">
         <v>5.3</v>
@@ -1104,17 +1104,17 @@
         <v>5.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.2</v>
+        <v>34</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
         <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
@@ -1372,13 +1372,13 @@
         <v>1.62</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="R5" t="n">
         <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T5" t="n">
         <v>2.26</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
         <v>1.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R7" t="n">
         <v>1.25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H8" t="n">
         <v>5.2</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="O9" t="n">
         <v>1.46</v>
@@ -2154,7 +2154,7 @@
         <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T9" t="n">
         <v>2.26</v>
@@ -2196,7 +2196,7 @@
         <v>9</v>
       </c>
       <c r="AG9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
         <v>34</v>
@@ -2229,10 +2229,10 @@
         <v>13.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT9" t="n">
         <v>4.9</v>
@@ -2241,10 +2241,10 @@
         <v>6.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX9" t="n">
         <v>6.6</v>
@@ -2256,29 +2256,29 @@
         <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.3</v>
+        <v>12.5</v>
       </c>
       <c r="BC9" t="n">
         <v>16.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF9" t="n">
         <v>11.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="G2" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="H2" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="I2" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="O2" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="P2" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="T2" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="U2" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="V2" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="X2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y2" t="n">
         <v>16</v>
       </c>
-      <c r="Y2" t="n">
-        <v>20</v>
-      </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK2" t="n">
         <v>23</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN2" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP2" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR2" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR2" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AS2" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV2" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.3</v>
+        <v>13.5</v>
       </c>
       <c r="AX2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE2" t="n">
         <v>7.4</v>
       </c>
-      <c r="AY2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC2" t="n">
+      <c r="BF2" t="n">
         <v>13</v>
       </c>
-      <c r="BD2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BG2" t="n">
-        <v>5.4</v>
+        <v>13</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -966,13 +966,13 @@
         <v>2.98</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N3" t="n">
         <v>2.7</v>
@@ -1008,7 +1008,7 @@
         <v>10.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z3" t="n">
         <v>23</v>
@@ -1017,16 +1017,16 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
         <v>20</v>
@@ -1044,7 +1044,7 @@
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1062,13 +1062,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT3" t="n">
         <v>7.6</v>
@@ -1080,7 +1080,7 @@
         <v>12</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.4</v>
+        <v>34</v>
       </c>
       <c r="AX3" t="n">
         <v>15</v>
@@ -1089,32 +1089,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>18.5</v>
+        <v>4.9</v>
       </c>
       <c r="BA3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>36</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG3" t="n">
         <v>5.5</v>
       </c>
-      <c r="BB3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>34</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -1148,22 +1148,22 @@
         <v>1.35</v>
       </c>
       <c r="G4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="H4" t="n">
         <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K4" t="n">
         <v>5.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1187,7 +1187,7 @@
         <v>3.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U4" t="n">
         <v>1.6</v>
@@ -1211,10 +1211,10 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AD4" t="n">
         <v>55</v>
@@ -1223,10 +1223,10 @@
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
         <v>42</v>
@@ -1235,10 +1235,10 @@
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
         <v>65</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT4" t="n">
         <v>5.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BG4" t="n">
-        <v>85</v>
+        <v>5.3</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -1369,28 +1369,28 @@
         <v>1.46</v>
       </c>
       <c r="P5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="R5" t="n">
         <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V5" t="n">
         <v>1.12</v>
       </c>
       <c r="W5" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="X5" t="n">
         <v>12.5</v>
@@ -1417,10 +1417,10 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AG5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH5" t="n">
         <v>38</v>
@@ -1429,13 +1429,13 @@
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
@@ -1453,10 +1453,10 @@
         <v>13.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT5" t="n">
         <v>4.6</v>
@@ -1465,10 +1465,10 @@
         <v>6.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX5" t="n">
         <v>6.2</v>
@@ -1477,10 +1477,10 @@
         <v>7.8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB5" t="n">
         <v>11.5</v>
@@ -1489,20 +1489,20 @@
         <v>15.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF5" t="n">
         <v>10.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>85</v>
+        <v>4.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -1533,28 +1533,28 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G6" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="H6" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.5</v>
       </c>
       <c r="M6" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N6" t="n">
         <v>2.42</v>
@@ -1563,28 +1563,28 @@
         <v>1.52</v>
       </c>
       <c r="P6" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S6" t="n">
         <v>4.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W6" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1599,7 +1599,7 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
         <v>1000</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.14</v>
+        <v>3.7</v>
       </c>
       <c r="AR6" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.12</v>
+        <v>5</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.02</v>
+        <v>3.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.1</v>
+        <v>4.9</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.89</v>
+        <v>3.9</v>
       </c>
       <c r="AY6" t="n">
-        <v>2.14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.99</v>
+        <v>4.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.04</v>
+        <v>4.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.04</v>
+        <v>4.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.08</v>
+        <v>4.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.04</v>
+        <v>4.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.12</v>
+        <v>5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H7" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="I7" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O7" t="n">
         <v>1.41</v>
@@ -1766,7 +1766,7 @@
         <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="T7" t="n">
         <v>1.86</v>
@@ -1775,7 +1775,7 @@
         <v>1.94</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W7" t="n">
         <v>1.5</v>
@@ -1787,13 +1787,13 @@
         <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA7" t="n">
         <v>65</v>
       </c>
       <c r="AB7" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
         <v>970</v>
@@ -1817,80 +1817,80 @@
         <v>65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AK7" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AL7" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO7" t="n">
         <v>50</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.22</v>
+        <v>4.6</v>
       </c>
       <c r="AT7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF7" t="n">
         <v>4.4</v>
       </c>
-      <c r="AU7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>6</v>
-      </c>
       <c r="BG7" t="n">
-        <v>2.62</v>
+        <v>4.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="G8" t="n">
         <v>1.99</v>
@@ -1930,16 +1930,16 @@
         <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
         <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="M8" t="n">
         <v>1.12</v>
@@ -1954,7 +1954,7 @@
         <v>1.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
@@ -1969,28 +1969,28 @@
         <v>1.66</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
         <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y8" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Z8" t="n">
         <v>44</v>
       </c>
       <c r="AA8" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD8" t="n">
         <v>25</v>
@@ -2011,16 +2011,16 @@
         <v>150</v>
       </c>
       <c r="AJ8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK8" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AL8" t="n">
         <v>70</v>
       </c>
       <c r="AM8" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AN8" t="n">
         <v>25</v>
@@ -2032,25 +2032,25 @@
         <v>7.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU8" t="n">
         <v>6.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AX8" t="n">
         <v>8.4</v>
@@ -2059,32 +2059,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>23</v>
+        <v>6.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BC8" t="n">
-        <v>20</v>
+        <v>6.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -2121,19 +2121,19 @@
         <v>1.74</v>
       </c>
       <c r="H9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I9" t="n">
         <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
         <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
@@ -2145,16 +2145,16 @@
         <v>1.46</v>
       </c>
       <c r="P9" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S9" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="T9" t="n">
         <v>2.26</v>
@@ -2172,19 +2172,19 @@
         <v>12</v>
       </c>
       <c r="Y9" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD9" t="n">
         <v>34</v>
@@ -2196,7 +2196,7 @@
         <v>9</v>
       </c>
       <c r="AG9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
         <v>34</v>
@@ -2205,10 +2205,10 @@
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL9" t="n">
         <v>1000</v>
@@ -2217,7 +2217,7 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
@@ -2229,10 +2229,10 @@
         <v>13.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT9" t="n">
         <v>4.9</v>
@@ -2241,44 +2241,44 @@
         <v>6.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.9</v>
+        <v>21</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AX9" t="n">
         <v>6.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17.5</v>
+        <v>6</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BB9" t="n">
         <v>12.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF9" t="n">
         <v>11.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -757,25 +757,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
         <v>3.65</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
@@ -808,7 +808,7 @@
         <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X2" t="n">
         <v>11</v>
@@ -856,7 +856,7 @@
         <v>60</v>
       </c>
       <c r="AM2" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AN2" t="n">
         <v>1000</v>
@@ -886,10 +886,10 @@
         <v>19.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY2" t="n">
         <v>9</v>
@@ -901,7 +901,7 @@
         <v>12.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>15.5</v>
+        <v>8.4</v>
       </c>
       <c r="BC2" t="n">
         <v>18.5</v>
@@ -910,7 +910,7 @@
         <v>12</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF2" t="n">
         <v>13</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
@@ -981,10 +981,10 @@
         <v>1.51</v>
       </c>
       <c r="P3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R3" t="n">
         <v>1.21</v>
@@ -1011,7 +1011,7 @@
         <v>9.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1065,10 +1065,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT3" t="n">
         <v>7.6</v>
@@ -1089,32 +1089,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.6</v>
+        <v>50</v>
       </c>
       <c r="BB3" t="n">
         <v>36</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG3" t="n">
         <v>5.6</v>
       </c>
-      <c r="BE3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>1.6</v>
       </c>
       <c r="G5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="H5" t="n">
         <v>7</v>
@@ -1357,7 +1357,7 @@
         <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
@@ -1369,10 +1369,10 @@
         <v>1.46</v>
       </c>
       <c r="P5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="R5" t="n">
         <v>1.22</v>
@@ -1390,7 +1390,7 @@
         <v>1.12</v>
       </c>
       <c r="W5" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="X5" t="n">
         <v>12.5</v>
@@ -1417,7 +1417,7 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG5" t="n">
         <v>13</v>
@@ -1453,10 +1453,10 @@
         <v>13.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AT5" t="n">
         <v>4.6</v>
@@ -1465,10 +1465,10 @@
         <v>6.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AX5" t="n">
         <v>6.2</v>
@@ -1477,10 +1477,10 @@
         <v>7.8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB5" t="n">
         <v>11.5</v>
@@ -1489,20 +1489,20 @@
         <v>15.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BF5" t="n">
         <v>10.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>2.18</v>
       </c>
       <c r="G6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H6" t="n">
         <v>3.35</v>
@@ -1665,7 +1665,7 @@
         <v>4.9</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY6" t="n">
         <v>8.800000000000001</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>2.62</v>
       </c>
       <c r="G7" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H7" t="n">
         <v>2.96</v>
@@ -1739,10 +1739,10 @@
         <v>3.35</v>
       </c>
       <c r="J7" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="L7" t="n">
         <v>1.42</v>
@@ -1760,13 +1760,13 @@
         <v>1.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="R7" t="n">
         <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="T7" t="n">
         <v>1.86</v>
@@ -1778,7 +1778,7 @@
         <v>1.42</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -1787,7 +1787,7 @@
         <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA7" t="n">
         <v>65</v>
@@ -1796,7 +1796,7 @@
         <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD7" t="n">
         <v>970</v>
@@ -1820,7 +1820,7 @@
         <v>50</v>
       </c>
       <c r="AK7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL7" t="n">
         <v>65</v>
@@ -1841,10 +1841,10 @@
         <v>7.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT7" t="n">
         <v>7.6</v>
@@ -1859,7 +1859,7 @@
         <v>4.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AY7" t="n">
         <v>3.8</v>
@@ -1868,29 +1868,29 @@
         <v>4.1</v>
       </c>
       <c r="BA7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB7" t="n">
         <v>4.6</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.5</v>
       </c>
       <c r="BC7" t="n">
         <v>4.5</v>
       </c>
       <c r="BD7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG7" t="n">
         <v>4.6</v>
       </c>
-      <c r="BE7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
@@ -1924,22 +1924,22 @@
         <v>1.9</v>
       </c>
       <c r="G8" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H8" t="n">
         <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="J8" t="n">
         <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L8" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="M8" t="n">
         <v>1.12</v>
@@ -1954,7 +1954,7 @@
         <v>1.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
@@ -1972,13 +1972,13 @@
         <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X8" t="n">
         <v>9</v>
       </c>
       <c r="Y8" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z8" t="n">
         <v>44</v>
@@ -2035,10 +2035,10 @@
         <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT8" t="n">
         <v>5.6</v>
@@ -2050,7 +2050,7 @@
         <v>19.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AX8" t="n">
         <v>8.4</v>
@@ -2059,32 +2059,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB8" t="n">
         <v>19</v>
       </c>
       <c r="BC8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD8" t="n">
         <v>50</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF8" t="n">
         <v>18</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -757,31 +757,31 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G2" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H2" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J2" t="n">
         <v>3.65</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="O2" t="n">
         <v>1.47</v>
@@ -790,7 +790,7 @@
         <v>1.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R2" t="n">
         <v>1.23</v>
@@ -805,22 +805,22 @@
         <v>1.74</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W2" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X2" t="n">
         <v>11</v>
       </c>
       <c r="Y2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z2" t="n">
         <v>46</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB2" t="n">
         <v>6.4</v>
@@ -832,7 +832,7 @@
         <v>23</v>
       </c>
       <c r="AE2" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
         <v>9.4</v>
@@ -853,7 +853,7 @@
         <v>23</v>
       </c>
       <c r="AL2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
         <v>240</v>
@@ -862,7 +862,7 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AP2" t="n">
         <v>10.5</v>
@@ -874,7 +874,7 @@
         <v>11.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="AT2" t="n">
         <v>5.7</v>
@@ -883,13 +883,13 @@
         <v>8</v>
       </c>
       <c r="AV2" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AW2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AY2" t="n">
         <v>9</v>
@@ -898,10 +898,10 @@
         <v>20</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.4</v>
+        <v>16</v>
       </c>
       <c r="BC2" t="n">
         <v>18.5</v>
@@ -910,17 +910,17 @@
         <v>12</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.6</v>
+        <v>3.5</v>
       </c>
       <c r="BF2" t="n">
         <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>13</v>
+        <v>4.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 10:30:55</t>
+          <t>2026-03-25 12:35:31</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         <v>2.96</v>
       </c>
       <c r="I3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J3" t="n">
         <v>2.98</v>
@@ -984,7 +984,7 @@
         <v>1.57</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
         <v>1.21</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 10:30:55</t>
+          <t>2026-03-25 12:35:31</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>1.35</v>
       </c>
       <c r="G4" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="H4" t="n">
         <v>11</v>
@@ -1157,13 +1157,13 @@
         <v>15.5</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="K4" t="n">
         <v>5.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1196,7 +1196,7 @@
         <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="X4" t="n">
         <v>17</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 10:30:55</t>
+          <t>2026-03-25 12:35:31</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>1.6</v>
       </c>
       <c r="G5" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="H5" t="n">
         <v>7</v>
@@ -1351,10 +1351,10 @@
         <v>9</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="L5" t="n">
         <v>1.42</v>
@@ -1372,25 +1372,25 @@
         <v>1.62</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="R5" t="n">
         <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="U5" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V5" t="n">
         <v>1.12</v>
       </c>
       <c r="W5" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="X5" t="n">
         <v>12.5</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 10:30:55</t>
+          <t>2026-03-25 12:35:31</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="H6" t="n">
         <v>3.35</v>
@@ -1545,7 +1545,7 @@
         <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
         <v>3.8</v>
@@ -1557,7 +1557,7 @@
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="O6" t="n">
         <v>1.52</v>
@@ -1584,7 +1584,7 @@
         <v>1.31</v>
       </c>
       <c r="W6" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1641,19 +1641,19 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AR6" t="n">
         <v>4.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AU6" t="n">
         <v>3.25</v>
@@ -1662,7 +1662,7 @@
         <v>4.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX6" t="n">
         <v>9.800000000000001</v>
@@ -1671,32 +1671,32 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BA6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD6" t="n">
         <v>5</v>
       </c>
-      <c r="BB6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BE6" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-25 10:30:55</t>
+          <t>2026-03-25 12:35:31</t>
         </is>
       </c>
     </row>
@@ -1733,16 +1733,16 @@
         <v>2.96</v>
       </c>
       <c r="H7" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="I7" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.42</v>
@@ -1760,7 +1760,7 @@
         <v>1.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
         <v>1.25</v>
@@ -1775,7 +1775,7 @@
         <v>1.94</v>
       </c>
       <c r="V7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W7" t="n">
         <v>1.51</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-25 10:30:55</t>
+          <t>2026-03-25 12:35:31</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>1.9</v>
       </c>
       <c r="G8" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="H8" t="n">
         <v>5.2</v>
@@ -1933,7 +1933,7 @@
         <v>5.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K8" t="n">
         <v>3.45</v>
@@ -1948,13 +1948,13 @@
         <v>2.56</v>
       </c>
       <c r="O8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P8" t="n">
         <v>1.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
@@ -1972,19 +1972,19 @@
         <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="X8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y8" t="n">
         <v>14</v>
       </c>
       <c r="Z8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA8" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB8" t="n">
         <v>6.6</v>
@@ -2014,13 +2014,13 @@
         <v>24</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL8" t="n">
         <v>70</v>
       </c>
       <c r="AM8" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN8" t="n">
         <v>25</v>
@@ -2029,16 +2029,16 @@
         <v>230</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ8" t="n">
         <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT8" t="n">
         <v>5.6</v>
@@ -2050,7 +2050,7 @@
         <v>19.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX8" t="n">
         <v>8.4</v>
@@ -2059,32 +2059,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB8" t="n">
         <v>19</v>
       </c>
       <c r="BC8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD8" t="n">
         <v>50</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF8" t="n">
         <v>18</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-25 10:30:55</t>
+          <t>2026-03-25 12:35:31</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
         <v>1.46</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q9" t="n">
         <v>2.36</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-25 10:30:55</t>
+          <t>2026-03-25 12:35:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -760,7 +760,7 @@
         <v>1.73</v>
       </c>
       <c r="G2" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="H2" t="n">
         <v>4.9</v>
@@ -769,19 +769,19 @@
         <v>6.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
         <v>4.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O2" t="n">
         <v>1.47</v>
@@ -799,16 +799,16 @@
         <v>4.7</v>
       </c>
       <c r="T2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U2" t="n">
         <v>1.74</v>
       </c>
       <c r="V2" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="X2" t="n">
         <v>11</v>
@@ -859,7 +859,7 @@
         <v>240</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO2" t="n">
         <v>180</v>
@@ -886,7 +886,7 @@
         <v>18</v>
       </c>
       <c r="AW2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AX2" t="n">
         <v>8.4</v>
@@ -895,32 +895,32 @@
         <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BB2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>18.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD2" t="n">
         <v>12</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="BF2" t="n">
         <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 12:35:31</t>
+          <t>2026-03-25 14:40:01</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 12:35:31</t>
+          <t>2026-03-25 14:40:01</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>1.35</v>
       </c>
       <c r="G4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="H4" t="n">
         <v>11</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 12:35:31</t>
+          <t>2026-03-25 14:40:01</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
         <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T5" t="n">
         <v>2.26</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 12:35:31</t>
+          <t>2026-03-25 14:40:01</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>2.2</v>
       </c>
       <c r="G6" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H6" t="n">
         <v>3.35</v>
@@ -1584,7 +1584,7 @@
         <v>1.31</v>
       </c>
       <c r="W6" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-25 12:35:31</t>
+          <t>2026-03-25 14:40:01</t>
         </is>
       </c>
     </row>
@@ -1730,19 +1730,19 @@
         <v>2.62</v>
       </c>
       <c r="G7" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="H7" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="I7" t="n">
         <v>3.3</v>
       </c>
       <c r="J7" t="n">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="L7" t="n">
         <v>1.42</v>
@@ -1778,7 +1778,7 @@
         <v>1.43</v>
       </c>
       <c r="W7" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-25 12:35:31</t>
+          <t>2026-03-25 14:40:01</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="G8" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>5.2</v>
@@ -1933,7 +1933,7 @@
         <v>5.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
         <v>3.45</v>
@@ -1972,7 +1972,7 @@
         <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
         <v>8.800000000000001</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-25 12:35:31</t>
+          <t>2026-03-25 14:40:01</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>1.63</v>
       </c>
       <c r="G9" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H9" t="n">
         <v>6.4</v>
@@ -2130,7 +2130,7 @@
         <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L9" t="n">
         <v>1.44</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-25 12:35:31</t>
+          <t>2026-03-25 14:40:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="G2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
         <v>6.2</v>
@@ -772,7 +772,7 @@
         <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
         <v>1.52</v>
@@ -808,7 +808,7 @@
         <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X2" t="n">
         <v>11</v>
@@ -871,7 +871,7 @@
         <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.5</v>
+        <v>34</v>
       </c>
       <c r="AS2" t="n">
         <v>4.4</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 14:40:01</t>
+          <t>2026-03-25 16:45:16</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="G3" t="n">
         <v>2.94</v>
@@ -960,13 +960,13 @@
         <v>2.96</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J3" t="n">
         <v>2.98</v>
       </c>
       <c r="K3" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -981,10 +981,10 @@
         <v>1.51</v>
       </c>
       <c r="P3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R3" t="n">
         <v>1.21</v>
@@ -993,13 +993,13 @@
         <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U3" t="n">
         <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W3" t="n">
         <v>1.52</v>
@@ -1107,14 +1107,14 @@
         <v>6</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.5</v>
+        <v>34</v>
       </c>
       <c r="BG3" t="n">
         <v>5.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 14:40:01</t>
+          <t>2026-03-25 16:45:16</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="G4" t="n">
         <v>1.4</v>
@@ -1154,46 +1154,46 @@
         <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K4" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="O4" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="R4" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="V4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W4" t="n">
         <v>3.5</v>
@@ -1211,7 +1211,7 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC4" t="n">
         <v>13.5</v>
@@ -1223,13 +1223,13 @@
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
@@ -1238,77 +1238,77 @@
         <v>12.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL4" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AU4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AY4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 14:40:01</t>
+          <t>2026-03-25 16:45:16</t>
         </is>
       </c>
     </row>
@@ -1378,13 +1378,13 @@
         <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T5" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V5" t="n">
         <v>1.12</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 14:40:01</t>
+          <t>2026-03-25 16:45:16</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>2.2</v>
       </c>
       <c r="G6" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H6" t="n">
         <v>3.35</v>
@@ -1584,7 +1584,7 @@
         <v>1.31</v>
       </c>
       <c r="W6" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-25 14:40:01</t>
+          <t>2026-03-25 16:45:16</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-25 14:40:01</t>
+          <t>2026-03-25 16:45:16</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
@@ -1930,7 +1930,7 @@
         <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J8" t="n">
         <v>3.2</v>
@@ -1945,7 +1945,7 @@
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="O8" t="n">
         <v>1.56</v>
@@ -1954,16 +1954,16 @@
         <v>1.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="T8" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U8" t="n">
         <v>1.66</v>
@@ -1978,55 +1978,55 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Y8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z8" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA8" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AB8" t="n">
         <v>6.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD8" t="n">
         <v>25</v>
       </c>
       <c r="AE8" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG8" t="n">
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="AI8" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK8" t="n">
         <v>29</v>
       </c>
       <c r="AL8" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AN8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO8" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AP8" t="n">
         <v>7.4</v>
@@ -2035,56 +2035,56 @@
         <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.6</v>
+        <v>42</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AU8" t="n">
         <v>6.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.4</v>
+        <v>38</v>
       </c>
       <c r="AX8" t="n">
         <v>8.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.8</v>
+        <v>24</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.4</v>
+        <v>42</v>
       </c>
       <c r="BB8" t="n">
         <v>19</v>
       </c>
       <c r="BC8" t="n">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="BD8" t="n">
         <v>50</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="BF8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.6</v>
+        <v>44</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-25 14:40:01</t>
+          <t>2026-03-25 16:45:16</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>3.95</v>
       </c>
       <c r="L9" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
@@ -2148,7 +2148,7 @@
         <v>1.61</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R9" t="n">
         <v>1.21</v>
@@ -2184,7 +2184,7 @@
         <v>6.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD9" t="n">
         <v>34</v>
@@ -2229,10 +2229,10 @@
         <v>13.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT9" t="n">
         <v>4.9</v>
@@ -2244,7 +2244,7 @@
         <v>21</v>
       </c>
       <c r="AW9" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AX9" t="n">
         <v>6.6</v>
@@ -2253,10 +2253,10 @@
         <v>8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB9" t="n">
         <v>12.5</v>
@@ -2265,20 +2265,20 @@
         <v>17</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE9" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF9" t="n">
         <v>11.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-25 14:40:01</t>
+          <t>2026-03-25 16:45:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -760,16 +760,16 @@
         <v>1.75</v>
       </c>
       <c r="G2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
         <v>3.95</v>
@@ -811,7 +811,7 @@
         <v>2.2</v>
       </c>
       <c r="X2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y2" t="n">
         <v>15</v>
@@ -874,7 +874,7 @@
         <v>34</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.4</v>
+        <v>12.5</v>
       </c>
       <c r="AT2" t="n">
         <v>5.7</v>
@@ -886,7 +886,7 @@
         <v>18</v>
       </c>
       <c r="AW2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX2" t="n">
         <v>8.4</v>
@@ -898,29 +898,29 @@
         <v>25</v>
       </c>
       <c r="BA2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB2" t="n">
         <v>16.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BF2" t="n">
         <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.3</v>
+        <v>12.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 16:45:16</t>
+          <t>2026-03-25 18:52:04</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
         <v>1.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R3" t="n">
         <v>1.21</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 16:45:16</t>
+          <t>2026-03-25 18:52:04</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H4" t="n">
         <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="J4" t="n">
         <v>4.8</v>
@@ -1175,28 +1175,28 @@
         <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
         <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U4" t="n">
         <v>1.66</v>
       </c>
       <c r="V4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>17</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 16:45:16</t>
+          <t>2026-03-25 18:52:04</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
         <v>3.95</v>
       </c>
       <c r="L5" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
@@ -1378,7 +1378,7 @@
         <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="T5" t="n">
         <v>2.3</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 16:45:16</t>
+          <t>2026-03-25 18:52:04</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>2.5</v>
       </c>
       <c r="H6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I6" t="n">
         <v>4.2</v>
@@ -1548,7 +1548,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
         <v>1.5</v>
@@ -1560,10 +1560,10 @@
         <v>2.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="P6" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="Q6" t="n">
         <v>2.38</v>
@@ -1575,10 +1575,10 @@
         <v>4.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="V6" t="n">
         <v>1.31</v>
@@ -1602,7 +1602,7 @@
         <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1686,7 +1686,7 @@
         <v>5</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.86</v>
+        <v>4.3</v>
       </c>
       <c r="BF6" t="n">
         <v>4.7</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-25 16:45:16</t>
+          <t>2026-03-25 18:52:04</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H7" t="n">
         <v>3.1</v>
@@ -1739,10 +1739,10 @@
         <v>3.3</v>
       </c>
       <c r="J7" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
         <v>1.42</v>
@@ -1760,7 +1760,7 @@
         <v>1.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="R7" t="n">
         <v>1.25</v>
@@ -1769,7 +1769,7 @@
         <v>4.1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
         <v>1.94</v>
@@ -1778,7 +1778,7 @@
         <v>1.43</v>
       </c>
       <c r="W7" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -1835,62 +1835,62 @@
         <v>50</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.199999999999999</v>
+        <v>3.85</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.8</v>
+        <v>3.9</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.6</v>
+        <v>3.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="AV7" t="n">
         <v>10</v>
       </c>
       <c r="AW7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>4.5</v>
       </c>
-      <c r="AX7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BA7" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.9</v>
+        <v>3.95</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-25 16:45:16</t>
+          <t>2026-03-25 18:52:04</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
@@ -1930,7 +1930,7 @@
         <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J8" t="n">
         <v>3.2</v>
@@ -1939,13 +1939,13 @@
         <v>3.45</v>
       </c>
       <c r="L8" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="M8" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N8" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
         <v>1.56</v>
@@ -1954,19 +1954,19 @@
         <v>1.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U8" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V8" t="n">
         <v>1.22</v>
@@ -1975,13 +1975,13 @@
         <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y8" t="n">
         <v>13</v>
       </c>
       <c r="Z8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA8" t="n">
         <v>180</v>
@@ -2005,13 +2005,13 @@
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AI8" t="n">
         <v>140</v>
       </c>
       <c r="AJ8" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AK8" t="n">
         <v>29</v>
@@ -2041,13 +2041,13 @@
         <v>42</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU8" t="n">
         <v>6.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AW8" t="n">
         <v>38</v>
@@ -2059,7 +2059,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA8" t="n">
         <v>42</v>
@@ -2068,7 +2068,7 @@
         <v>19</v>
       </c>
       <c r="BC8" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="BD8" t="n">
         <v>50</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-25 16:45:16</t>
+          <t>2026-03-25 18:52:04</t>
         </is>
       </c>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="G9" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="H9" t="n">
         <v>6.4</v>
@@ -2127,19 +2127,19 @@
         <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="K9" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
         <v>1.46</v>
@@ -2166,16 +2166,16 @@
         <v>1.14</v>
       </c>
       <c r="W9" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="X9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y9" t="n">
         <v>18.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
@@ -2187,7 +2187,7 @@
         <v>9</v>
       </c>
       <c r="AD9" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
@@ -2229,10 +2229,10 @@
         <v>13.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT9" t="n">
         <v>4.9</v>
@@ -2244,7 +2244,7 @@
         <v>21</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX9" t="n">
         <v>6.6</v>
@@ -2253,10 +2253,10 @@
         <v>8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB9" t="n">
         <v>12.5</v>
@@ -2265,20 +2265,20 @@
         <v>17</v>
       </c>
       <c r="BD9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF9" t="n">
         <v>11.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-25 16:45:16</t>
+          <t>2026-03-25 18:52:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -757,37 +757,37 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="G2" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="H2" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="I2" t="n">
         <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O2" t="n">
         <v>1.47</v>
       </c>
       <c r="P2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q2" t="n">
         <v>2.32</v>
@@ -805,10 +805,10 @@
         <v>1.74</v>
       </c>
       <c r="V2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="X2" t="n">
         <v>12</v>
@@ -817,10 +817,10 @@
         <v>15</v>
       </c>
       <c r="Z2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA2" t="n">
-        <v>190</v>
+        <v>900</v>
       </c>
       <c r="AB2" t="n">
         <v>6.4</v>
@@ -832,7 +832,7 @@
         <v>23</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AF2" t="n">
         <v>9.4</v>
@@ -859,7 +859,7 @@
         <v>240</v>
       </c>
       <c r="AN2" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO2" t="n">
         <v>180</v>
@@ -868,59 +868,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR2" t="n">
         <v>34</v>
       </c>
       <c r="AS2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT2" t="n">
         <v>5.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX2" t="n">
         <v>8.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
         <v>25</v>
       </c>
       <c r="BA2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>16.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD2" t="n">
         <v>11</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.2</v>
+        <v>13.5</v>
       </c>
       <c r="BF2" t="n">
         <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="G3" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H3" t="n">
         <v>2.96</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J3" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -975,7 +975,7 @@
         <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="O3" t="n">
         <v>1.51</v>
@@ -984,7 +984,7 @@
         <v>1.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="R3" t="n">
         <v>1.21</v>
@@ -1008,25 +1008,25 @@
         <v>10.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z3" t="n">
         <v>22</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB3" t="n">
         <v>10</v>
       </c>
       <c r="AC3" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AD3" t="n">
         <v>16.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AF3" t="n">
         <v>20</v>
@@ -1041,7 +1041,7 @@
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK3" t="n">
         <v>46</v>
@@ -1065,10 +1065,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.7</v>
+        <v>20</v>
       </c>
       <c r="AT3" t="n">
         <v>7.6</v>
@@ -1089,7 +1089,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5</v>
+        <v>18.5</v>
       </c>
       <c r="BA3" t="n">
         <v>50</v>
@@ -1098,23 +1098,23 @@
         <v>36</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE3" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>34</v>
+        <v>7.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -1148,19 +1148,19 @@
         <v>1.33</v>
       </c>
       <c r="G4" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="H4" t="n">
         <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="J4" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="K4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.33</v>
@@ -1169,7 +1169,7 @@
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O4" t="n">
         <v>1.29</v>
@@ -1178,7 +1178,7 @@
         <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R4" t="n">
         <v>1.37</v>
@@ -1193,28 +1193,28 @@
         <v>1.66</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="X4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD4" t="n">
         <v>55</v>
@@ -1223,25 +1223,25 @@
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AK4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
@@ -1256,25 +1256,25 @@
         <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.1</v>
+        <v>13</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AU4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.4</v>
+        <v>32</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="AX4" t="n">
         <v>5.9</v>
@@ -1283,10 +1283,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.2</v>
+        <v>18</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="BB4" t="n">
         <v>8.199999999999999</v>
@@ -1295,20 +1295,20 @@
         <v>12.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF4" t="n">
         <v>5.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.9</v>
+        <v>15</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H5" t="n">
         <v>7</v>
@@ -1354,16 +1354,16 @@
         <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="O5" t="n">
         <v>1.46</v>
@@ -1375,7 +1375,7 @@
         <v>2.36</v>
       </c>
       <c r="R5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S5" t="n">
         <v>4.5</v>
@@ -1390,34 +1390,34 @@
         <v>1.12</v>
       </c>
       <c r="W5" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="X5" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y5" t="n">
         <v>23</v>
       </c>
       <c r="Z5" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AC5" t="n">
         <v>11</v>
       </c>
       <c r="AD5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG5" t="n">
         <v>13</v>
@@ -1432,16 +1432,16 @@
         <v>19.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
@@ -1450,59 +1450,59 @@
         <v>7.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AU5" t="n">
         <v>6.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.1</v>
+        <v>15.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.1</v>
+        <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BB5" t="n">
         <v>11.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BF5" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
         <v>1.5</v>
@@ -1560,13 +1560,13 @@
         <v>2.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="P6" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="R6" t="n">
         <v>1.19</v>
@@ -1578,16 +1578,16 @@
         <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V6" t="n">
         <v>1.31</v>
       </c>
       <c r="W6" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y6" t="n">
         <v>1000</v>
@@ -1599,10 +1599,10 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>42</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1641,28 +1641,28 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.5</v>
+        <v>2.84</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.1</v>
+        <v>2.92</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.25</v>
+        <v>2.58</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.2</v>
+        <v>2.68</v>
       </c>
       <c r="AW6" t="n">
-        <v>5</v>
+        <v>2.72</v>
       </c>
       <c r="AX6" t="n">
         <v>9.800000000000001</v>
@@ -1671,32 +1671,32 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.5</v>
+        <v>2.66</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.1</v>
+        <v>2.94</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.7</v>
+        <v>3.65</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.7</v>
+        <v>2.72</v>
       </c>
       <c r="BD6" t="n">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.1</v>
+        <v>3.05</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="G7" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J7" t="n">
         <v>3.1</v>
       </c>
-      <c r="I7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.05</v>
-      </c>
       <c r="K7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L7" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
         <v>1.41</v>
@@ -1766,131 +1766,131 @@
         <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U7" t="n">
         <v>1.94</v>
       </c>
       <c r="V7" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
         <v>1.56</v>
       </c>
       <c r="X7" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="Z7" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AA7" t="n">
-        <v>65</v>
+        <v>320</v>
       </c>
       <c r="AB7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="AD7" t="n">
         <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="AI7" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>50</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS7" t="n">
         <v>40</v>
       </c>
-      <c r="AL7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
+      <c r="AT7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA7" t="n">
         <v>40</v>
       </c>
-      <c r="AO7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV7" t="n">
+      <c r="BB7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE7" t="n">
         <v>10</v>
       </c>
-      <c r="AW7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BF7" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.2</v>
+        <v>32</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J8" t="n">
         <v>3.2</v>
@@ -1939,13 +1939,13 @@
         <v>3.45</v>
       </c>
       <c r="L8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M8" t="n">
         <v>1.13</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O8" t="n">
         <v>1.56</v>
@@ -1993,7 +1993,7 @@
         <v>7.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
@@ -2005,7 +2005,7 @@
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AI8" t="n">
         <v>140</v>
@@ -2023,7 +2023,7 @@
         <v>260</v>
       </c>
       <c r="AN8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO8" t="n">
         <v>210</v>
@@ -2059,7 +2059,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BA8" t="n">
         <v>42</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G9" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H9" t="n">
         <v>6.4</v>
@@ -2127,13 +2127,13 @@
         <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
         <v>3.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
@@ -2166,7 +2166,7 @@
         <v>1.14</v>
       </c>
       <c r="W9" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X9" t="n">
         <v>11.5</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G2" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H2" t="n">
         <v>5.5</v>
@@ -775,22 +775,22 @@
         <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O2" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="P2" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
         <v>1.23</v>
@@ -799,10 +799,10 @@
         <v>4.7</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V2" t="n">
         <v>1.2</v>
@@ -817,7 +817,7 @@
         <v>15</v>
       </c>
       <c r="Z2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA2" t="n">
         <v>900</v>
@@ -847,7 +847,7 @@
         <v>140</v>
       </c>
       <c r="AJ2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK2" t="n">
         <v>23</v>
@@ -856,10 +856,10 @@
         <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AN2" t="n">
-        <v>16.5</v>
+        <v>85</v>
       </c>
       <c r="AO2" t="n">
         <v>180</v>
@@ -874,7 +874,7 @@
         <v>34</v>
       </c>
       <c r="AS2" t="n">
-        <v>13</v>
+        <v>4.2</v>
       </c>
       <c r="AT2" t="n">
         <v>5.7</v>
@@ -883,10 +883,10 @@
         <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>18.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX2" t="n">
         <v>8.4</v>
@@ -895,32 +895,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BC2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF2" t="n">
         <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -978,13 +978,13 @@
         <v>2.74</v>
       </c>
       <c r="O3" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P3" t="n">
         <v>1.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R3" t="n">
         <v>1.21</v>
@@ -1020,13 +1020,13 @@
         <v>10</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AD3" t="n">
         <v>16.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
         <v>20</v>
@@ -1098,23 +1098,23 @@
         <v>36</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BD3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BE3" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BF3" t="n">
-        <v>7.8</v>
+        <v>34</v>
       </c>
       <c r="BG3" t="n">
         <v>8.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -1154,28 +1154,28 @@
         <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="J4" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K4" t="n">
         <v>5.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O4" t="n">
         <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q4" t="n">
         <v>1.84</v>
@@ -1190,10 +1190,10 @@
         <v>2.24</v>
       </c>
       <c r="U4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V4" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W4" t="n">
         <v>3.85</v>
@@ -1223,7 +1223,7 @@
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AG4" t="n">
         <v>11</v>
@@ -1247,7 +1247,7 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
@@ -1256,13 +1256,13 @@
         <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AT4" t="n">
         <v>6.2</v>
@@ -1274,7 +1274,7 @@
         <v>32</v>
       </c>
       <c r="AW4" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX4" t="n">
         <v>5.9</v>
@@ -1283,10 +1283,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB4" t="n">
         <v>8.199999999999999</v>
@@ -1295,10 +1295,10 @@
         <v>12.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF4" t="n">
         <v>5.4</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>2.16</v>
       </c>
       <c r="G6" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H6" t="n">
         <v>3.75</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G7" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="H7" t="n">
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J7" t="n">
         <v>3.1</v>
@@ -1745,7 +1745,7 @@
         <v>3.55</v>
       </c>
       <c r="L7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
@@ -1757,7 +1757,7 @@
         <v>1.41</v>
       </c>
       <c r="P7" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q7" t="n">
         <v>2.22</v>
@@ -1775,7 +1775,7 @@
         <v>1.94</v>
       </c>
       <c r="V7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W7" t="n">
         <v>1.56</v>
@@ -1793,7 +1793,7 @@
         <v>320</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC7" t="n">
         <v>14</v>
@@ -1841,7 +1841,7 @@
         <v>9</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS7" t="n">
         <v>40</v>
@@ -1856,16 +1856,16 @@
         <v>11.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="AY7" t="n">
         <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BA7" t="n">
         <v>40</v>
@@ -1877,7 +1877,7 @@
         <v>8.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="BE7" t="n">
         <v>10</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="H8" t="n">
         <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L8" t="n">
         <v>1.59</v>
@@ -1945,16 +1945,16 @@
         <v>1.13</v>
       </c>
       <c r="N8" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="O8" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="P8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
@@ -1963,16 +1963,16 @@
         <v>5.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="U8" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="X8" t="n">
         <v>8.6</v>
@@ -1981,19 +1981,19 @@
         <v>13</v>
       </c>
       <c r="Z8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA8" t="n">
         <v>180</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
@@ -2005,13 +2005,13 @@
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AI8" t="n">
         <v>140</v>
       </c>
       <c r="AJ8" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AK8" t="n">
         <v>29</v>
@@ -2023,13 +2023,13 @@
         <v>260</v>
       </c>
       <c r="AN8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AO8" t="n">
         <v>210</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ8" t="n">
         <v>11</v>
@@ -2041,13 +2041,13 @@
         <v>42</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW8" t="n">
         <v>38</v>
@@ -2080,11 +2080,11 @@
         <v>20</v>
       </c>
       <c r="BG8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
         <v>6.4</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="J9" t="n">
         <v>3.45</v>
@@ -2142,28 +2142,28 @@
         <v>2.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P9" t="n">
         <v>1.61</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R9" t="n">
         <v>1.21</v>
       </c>
       <c r="S9" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="U9" t="n">
         <v>1.67</v>
       </c>
       <c r="V9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W9" t="n">
         <v>2.3</v>
@@ -2175,43 +2175,43 @@
         <v>18.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC9" t="n">
         <v>9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG9" t="n">
         <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AK9" t="n">
         <v>24</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS9" t="n">
         <v>8</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AT9" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV9" t="n">
         <v>21</v>
       </c>
       <c r="AW9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY9" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AX9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY9" t="n">
+      <c r="AZ9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE9" t="n">
         <v>8</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BF9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -760,7 +760,7 @@
         <v>1.72</v>
       </c>
       <c r="G2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="H2" t="n">
         <v>5.5</v>
@@ -769,7 +769,7 @@
         <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
         <v>4</v>
@@ -781,28 +781,28 @@
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
         <v>1.45</v>
       </c>
       <c r="P2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S2" t="n">
         <v>4.7</v>
       </c>
       <c r="T2" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U2" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V2" t="n">
         <v>1.2</v>
@@ -811,7 +811,7 @@
         <v>2.28</v>
       </c>
       <c r="X2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="Y2" t="n">
         <v>15</v>
@@ -853,13 +853,13 @@
         <v>23</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
         <v>230</v>
       </c>
       <c r="AN2" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AO2" t="n">
         <v>180</v>
@@ -874,16 +874,16 @@
         <v>34</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="AW2" t="n">
         <v>13.5</v>
@@ -895,19 +895,19 @@
         <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BA2" t="n">
         <v>13.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="BC2" t="n">
-        <v>9.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BE2" t="n">
         <v>14.5</v>
@@ -916,11 +916,11 @@
         <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
@@ -951,40 +951,40 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="G3" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H3" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I3" t="n">
         <v>3.15</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K3" t="n">
         <v>3.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M3" t="n">
         <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="O3" t="n">
         <v>1.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="R3" t="n">
         <v>1.21</v>
@@ -996,7 +996,7 @@
         <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V3" t="n">
         <v>1.47</v>
@@ -1023,7 +1023,7 @@
         <v>6.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
@@ -1035,13 +1035,13 @@
         <v>15.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AK3" t="n">
         <v>46</v>
@@ -1098,13 +1098,13 @@
         <v>36</v>
       </c>
       <c r="BC3" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD3" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF3" t="n">
         <v>34</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="G4" t="n">
         <v>1.35</v>
       </c>
       <c r="H4" t="n">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="I4" t="n">
-        <v>14</v>
+        <v>19.5</v>
       </c>
       <c r="J4" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="K4" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
         <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="R4" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S4" t="n">
         <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W4" t="n">
         <v>3.85</v>
       </c>
       <c r="X4" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>540</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>14</v>
+        <v>1.42</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14</v>
+        <v>4.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.6</v>
+        <v>4.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.2</v>
+        <v>1.41</v>
       </c>
       <c r="AU4" t="n">
-        <v>9.199999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>32</v>
+        <v>4.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>9.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.199999999999999</v>
+        <v>1.48</v>
       </c>
       <c r="AZ4" t="n">
-        <v>19.5</v>
+        <v>1.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>12.5</v>
+        <v>1.48</v>
       </c>
       <c r="BD4" t="n">
-        <v>8.199999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.4</v>
+        <v>1.63</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.4</v>
+        <v>2.34</v>
       </c>
       <c r="BG4" t="n">
-        <v>15</v>
+        <v>4.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="G5" t="n">
         <v>1.68</v>
@@ -1351,40 +1351,40 @@
         <v>9</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
         <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="O5" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P5" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="R5" t="n">
         <v>1.23</v>
       </c>
       <c r="S5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T5" t="n">
         <v>2.3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V5" t="n">
         <v>1.12</v>
@@ -1396,7 +1396,7 @@
         <v>11</v>
       </c>
       <c r="Y5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Z5" t="n">
         <v>160</v>
@@ -1432,16 +1432,16 @@
         <v>19.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL5" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
@@ -1453,10 +1453,10 @@
         <v>15.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT5" t="n">
         <v>5.2</v>
@@ -1465,10 +1465,10 @@
         <v>6.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="AW5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX5" t="n">
         <v>7</v>
@@ -1480,7 +1480,7 @@
         <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB5" t="n">
         <v>11.5</v>
@@ -1489,20 +1489,20 @@
         <v>18</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BE5" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF5" t="n">
         <v>12</v>
       </c>
       <c r="BG5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
@@ -1533,55 +1533,55 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="G6" t="n">
         <v>2.4</v>
       </c>
       <c r="H6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I6" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="O6" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="P6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="R6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S6" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U6" t="n">
         <v>1.79</v>
       </c>
       <c r="V6" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
         <v>1.72</v>
@@ -1641,25 +1641,25 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="AS6" t="n">
         <v>2.92</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="AW6" t="n">
         <v>2.72</v>
@@ -1671,13 +1671,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.66</v>
+        <v>2.96</v>
       </c>
       <c r="BA6" t="n">
         <v>2.94</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BC6" t="n">
         <v>2.72</v>
@@ -1686,17 +1686,17 @@
         <v>2.62</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
@@ -1727,58 +1727,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="G7" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="I7" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K7" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L7" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P7" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S7" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="U7" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V7" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W7" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="X7" t="n">
         <v>19.5</v>
@@ -1790,22 +1790,22 @@
         <v>500</v>
       </c>
       <c r="AA7" t="n">
-        <v>320</v>
+        <v>160</v>
       </c>
       <c r="AB7" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC7" t="n">
         <v>14</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AE7" t="n">
         <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
         <v>22</v>
@@ -1817,7 +1817,7 @@
         <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AK7" t="n">
         <v>500</v>
@@ -1838,16 +1838,16 @@
         <v>9.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9</v>
+        <v>5.9</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AS7" t="n">
         <v>40</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.8</v>
+        <v>5.5</v>
       </c>
       <c r="AU7" t="n">
         <v>6.4</v>
@@ -1856,31 +1856,31 @@
         <v>11.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AX7" t="n">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="AY7" t="n">
         <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BA7" t="n">
         <v>40</v>
       </c>
       <c r="BB7" t="n">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BF7" t="n">
         <v>6.2</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
@@ -1921,73 +1921,73 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="G8" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H8" t="n">
         <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J8" t="n">
         <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L8" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="M8" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N8" t="n">
         <v>2.56</v>
       </c>
       <c r="O8" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="P8" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S8" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="T8" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="U8" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
         <v>2.04</v>
       </c>
       <c r="X8" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="AA8" t="n">
         <v>180</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AC8" t="n">
         <v>8</v>
@@ -2005,10 +2005,10 @@
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AI8" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AJ8" t="n">
         <v>23</v>
@@ -2020,16 +2020,16 @@
         <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>260</v>
+        <v>330</v>
       </c>
       <c r="AN8" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AO8" t="n">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ8" t="n">
         <v>11</v>
@@ -2038,22 +2038,22 @@
         <v>30</v>
       </c>
       <c r="AS8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AU8" t="n">
         <v>7.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AW8" t="n">
         <v>38</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY8" t="n">
         <v>10.5</v>
@@ -2062,13 +2062,13 @@
         <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC8" t="n">
         <v>19</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>18.5</v>
       </c>
       <c r="BD8" t="n">
         <v>50</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="G9" t="n">
         <v>1.76</v>
       </c>
       <c r="H9" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="I9" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9" t="n">
         <v>3.45</v>
@@ -2133,37 +2133,37 @@
         <v>3.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O9" t="n">
         <v>1.47</v>
       </c>
       <c r="P9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="R9" t="n">
         <v>1.21</v>
       </c>
       <c r="S9" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U9" t="n">
         <v>1.67</v>
       </c>
       <c r="V9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W9" t="n">
         <v>2.3</v>
@@ -2175,7 +2175,7 @@
         <v>18.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
@@ -2199,7 +2199,7 @@
         <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="G2" t="n">
         <v>1.78</v>
@@ -769,7 +769,7 @@
         <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K2" t="n">
         <v>4</v>
@@ -781,7 +781,7 @@
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O2" t="n">
         <v>1.45</v>
@@ -790,19 +790,19 @@
         <v>1.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T2" t="n">
         <v>2.16</v>
       </c>
       <c r="U2" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V2" t="n">
         <v>1.2</v>
@@ -811,31 +811,31 @@
         <v>2.28</v>
       </c>
       <c r="X2" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="Y2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z2" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AA2" t="n">
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AE2" t="n">
-        <v>240</v>
+        <v>110</v>
       </c>
       <c r="AF2" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AG2" t="n">
         <v>10.5</v>
@@ -844,7 +844,7 @@
         <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
         <v>18</v>
@@ -853,16 +853,16 @@
         <v>23</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM2" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AN2" t="n">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="AO2" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AP2" t="n">
         <v>10.5</v>
@@ -874,53 +874,53 @@
         <v>34</v>
       </c>
       <c r="AS2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="AT2" t="n">
         <v>5.9</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AV2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AW2" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY2" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BB2" t="n">
         <v>16</v>
       </c>
       <c r="BC2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="BE2" t="n">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="BF2" t="n">
         <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="H3" t="n">
         <v>2.98</v>
@@ -975,10 +975,10 @@
         <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P3" t="n">
         <v>1.59</v>
@@ -993,13 +993,13 @@
         <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
         <v>1.86</v>
       </c>
       <c r="V3" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W3" t="n">
         <v>1.52</v>
@@ -1017,7 +1017,7 @@
         <v>130</v>
       </c>
       <c r="AB3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC3" t="n">
         <v>6.6</v>
@@ -1035,7 +1035,7 @@
         <v>15.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
@@ -1044,7 +1044,7 @@
         <v>55</v>
       </c>
       <c r="AK3" t="n">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1053,7 +1053,7 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
@@ -1065,13 +1065,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS3" t="n">
         <v>20</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU3" t="n">
         <v>6.2</v>
@@ -1098,13 +1098,13 @@
         <v>36</v>
       </c>
       <c r="BC3" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE3" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>9.6</v>
       </c>
       <c r="BF3" t="n">
         <v>34</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="G4" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H4" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="I4" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="K4" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
         <v>1.38</v>
@@ -1169,16 +1169,16 @@
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="R4" t="n">
         <v>1.39</v>
@@ -1187,22 +1187,22 @@
         <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="V4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Z4" t="n">
         <v>1000</v>
@@ -1211,104 +1211,104 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>29</v>
+        <v>6.2</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.42</v>
+        <v>13</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.41</v>
+        <v>6</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.6</v>
+        <v>10.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.48</v>
+        <v>8.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.6</v>
+        <v>18</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.48</v>
+        <v>12.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.44</v>
+        <v>9.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.63</v>
+        <v>11</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.34</v>
+        <v>5.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="G5" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="H5" t="n">
         <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L5" t="n">
         <v>1.52</v>
@@ -1366,10 +1366,10 @@
         <v>2.92</v>
       </c>
       <c r="O5" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P5" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q5" t="n">
         <v>2.4</v>
@@ -1378,28 +1378,28 @@
         <v>1.23</v>
       </c>
       <c r="S5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T5" t="n">
         <v>2.3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V5" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="W5" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="X5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z5" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
@@ -1408,10 +1408,10 @@
         <v>6.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
@@ -1423,13 +1423,13 @@
         <v>13</v>
       </c>
       <c r="AH5" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AK5" t="n">
         <v>22</v>
@@ -1441,7 +1441,7 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
@@ -1453,10 +1453,10 @@
         <v>15.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT5" t="n">
         <v>5.2</v>
@@ -1468,7 +1468,7 @@
         <v>22</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX5" t="n">
         <v>7</v>
@@ -1480,7 +1480,7 @@
         <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB5" t="n">
         <v>11.5</v>
@@ -1489,20 +1489,20 @@
         <v>18</v>
       </c>
       <c r="BD5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF5" t="n">
         <v>12</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H6" t="n">
         <v>3.7</v>
@@ -1557,37 +1557,37 @@
         <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="O6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P6" t="n">
         <v>1.54</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.55</v>
       </c>
       <c r="Q6" t="n">
         <v>2.66</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V6" t="n">
         <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X6" t="n">
-        <v>90</v>
+        <v>17.5</v>
       </c>
       <c r="Y6" t="n">
         <v>1000</v>
@@ -1599,7 +1599,7 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
         <v>42</v>
@@ -1623,10 +1623,10 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL6" t="n">
         <v>1000</v>
@@ -1641,28 +1641,28 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.15</v>
+        <v>2.02</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.92</v>
+        <v>2.14</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="AU6" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.72</v>
+        <v>2</v>
       </c>
       <c r="AX6" t="n">
         <v>9.800000000000001</v>
@@ -1671,32 +1671,32 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.96</v>
+        <v>2</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.94</v>
+        <v>2.1</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.72</v>
+        <v>2.06</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.55</v>
+        <v>2.04</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="H7" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
         <v>3.1</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.15</v>
-      </c>
       <c r="K7" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L7" t="n">
         <v>1.5</v>
@@ -1769,16 +1769,16 @@
         <v>4.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="U7" t="n">
         <v>1.96</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
         <v>19.5</v>
@@ -1790,10 +1790,10 @@
         <v>500</v>
       </c>
       <c r="AA7" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
         <v>14</v>
@@ -1808,7 +1808,7 @@
         <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
         <v>60</v>
@@ -1817,7 +1817,7 @@
         <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="AK7" t="n">
         <v>500</v>
@@ -1838,25 +1838,25 @@
         <v>9.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AS7" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AU7" t="n">
         <v>6.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AX7" t="n">
         <v>7.6</v>
@@ -1865,32 +1865,32 @@
         <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BA7" t="n">
         <v>40</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC7" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="BE7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG7" t="n">
-        <v>32</v>
+        <v>8.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -1921,46 +1921,46 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="G8" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I8" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L8" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="M8" t="n">
         <v>1.14</v>
       </c>
       <c r="N8" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="O8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="P8" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="R8" t="n">
         <v>1.17</v>
       </c>
       <c r="S8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T8" t="n">
         <v>2.42</v>
@@ -1972,16 +1972,16 @@
         <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z8" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AA8" t="n">
         <v>180</v>
@@ -1993,7 +1993,7 @@
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
@@ -2011,22 +2011,22 @@
         <v>170</v>
       </c>
       <c r="AJ8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AK8" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AL8" t="n">
         <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="AN8" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AO8" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AP8" t="n">
         <v>7.2</v>
@@ -2038,10 +2038,10 @@
         <v>30</v>
       </c>
       <c r="AS8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU8" t="n">
         <v>7.2</v>
@@ -2059,16 +2059,16 @@
         <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB8" t="n">
         <v>20</v>
       </c>
-      <c r="BA8" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BC8" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BD8" t="n">
         <v>50</v>
@@ -2077,14 +2077,14 @@
         <v>50</v>
       </c>
       <c r="BF8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG8" t="n">
         <v>46</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -2115,64 +2115,64 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G9" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="H9" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="I9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J9" t="n">
         <v>3.45</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L9" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N9" t="n">
         <v>2.84</v>
       </c>
       <c r="O9" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
         <v>1.21</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T9" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="U9" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="V9" t="n">
         <v>1.16</v>
       </c>
       <c r="W9" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="X9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
@@ -2181,25 +2181,25 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AC9" t="n">
         <v>9</v>
       </c>
       <c r="AD9" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG9" t="n">
         <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
@@ -2211,7 +2211,7 @@
         <v>24</v>
       </c>
       <c r="AL9" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
@@ -2229,10 +2229,10 @@
         <v>14</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT9" t="n">
         <v>5.4</v>
@@ -2244,7 +2244,7 @@
         <v>21</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AX9" t="n">
         <v>6.8</v>
@@ -2253,10 +2253,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BB9" t="n">
         <v>13</v>
@@ -2265,20 +2265,20 @@
         <v>17.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE9" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BG9" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -757,82 +757,82 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I2" t="n">
         <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P2" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="T2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U2" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="V2" t="n">
         <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y2" t="n">
         <v>16</v>
       </c>
       <c r="Z2" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AA2" t="n">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="AB2" t="n">
         <v>6.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD2" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AE2" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AF2" t="n">
         <v>9</v>
@@ -841,22 +841,22 @@
         <v>10.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AJ2" t="n">
         <v>18</v>
       </c>
       <c r="AK2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL2" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AN2" t="n">
         <v>16</v>
@@ -865,19 +865,19 @@
         <v>170</v>
       </c>
       <c r="AP2" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR2" t="n">
         <v>34</v>
       </c>
       <c r="AS2" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU2" t="n">
         <v>8</v>
@@ -886,7 +886,7 @@
         <v>21</v>
       </c>
       <c r="AW2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX2" t="n">
         <v>8.199999999999999</v>
@@ -898,29 +898,29 @@
         <v>24</v>
       </c>
       <c r="BA2" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC2" t="n">
         <v>19.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="BE2" t="n">
-        <v>28</v>
+        <v>16.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BG2" t="n">
         <v>15</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G3" t="n">
         <v>2.92</v>
@@ -963,10 +963,10 @@
         <v>3.15</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L3" t="n">
         <v>1.55</v>
@@ -981,25 +981,25 @@
         <v>1.51</v>
       </c>
       <c r="P3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q3" t="n">
         <v>2.54</v>
       </c>
       <c r="R3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="V3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W3" t="n">
         <v>1.52</v>
@@ -1017,7 +1017,7 @@
         <v>130</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC3" t="n">
         <v>6.6</v>
@@ -1038,16 +1038,16 @@
         <v>55</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ3" t="n">
         <v>55</v>
       </c>
       <c r="AK3" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1056,13 +1056,13 @@
         <v>55</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR3" t="n">
         <v>9.199999999999999</v>
@@ -1083,7 +1083,7 @@
         <v>34</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>7.6</v>
       </c>
       <c r="AY3" t="n">
         <v>11.5</v>
@@ -1101,20 +1101,20 @@
         <v>16</v>
       </c>
       <c r="BD3" t="n">
-        <v>29</v>
+        <v>9.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>34</v>
+        <v>8.4</v>
       </c>
       <c r="BG3" t="n">
         <v>8.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -1145,109 +1145,109 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>13</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O4" t="n">
         <v>1.31</v>
       </c>
-      <c r="G4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="H4" t="n">
-        <v>12</v>
-      </c>
-      <c r="I4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.28</v>
-      </c>
       <c r="P4" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="R4" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T4" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="U4" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="V4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W4" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="X4" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Y4" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>760</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AF4" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AK4" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
@@ -1256,59 +1256,59 @@
         <v>13</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU4" t="n">
         <v>10.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="AW4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="BA4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>9.6</v>
+        <v>28</v>
       </c>
       <c r="BE4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -1339,76 +1339,76 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H5" t="n">
         <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J5" t="n">
         <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="P5" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="R5" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="S5" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="U5" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="V5" t="n">
         <v>1.15</v>
       </c>
       <c r="W5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="X5" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y5" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD5" t="n">
         <v>32</v>
@@ -1420,7 +1420,7 @@
         <v>8.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH5" t="n">
         <v>32</v>
@@ -1429,37 +1429,37 @@
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AU5" t="n">
         <v>6.6</v>
@@ -1468,7 +1468,7 @@
         <v>22</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="AX5" t="n">
         <v>7</v>
@@ -1480,29 +1480,29 @@
         <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BB5" t="n">
         <v>11.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="BF5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -1533,58 +1533,58 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G6" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
         <v>3.05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L6" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="M6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.68</v>
+        <v>2.94</v>
       </c>
       <c r="O6" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="P6" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.66</v>
+        <v>2.42</v>
       </c>
       <c r="R6" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="U6" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="V6" t="n">
         <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="X6" t="n">
         <v>17.5</v>
@@ -1602,7 +1602,7 @@
         <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1626,7 +1626,7 @@
         <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
         <v>1000</v>
@@ -1641,28 +1641,28 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.86</v>
+        <v>6.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="AW6" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="AX6" t="n">
         <v>9.800000000000001</v>
@@ -1671,32 +1671,32 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2</v>
+        <v>3.45</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.04</v>
+        <v>4.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.85</v>
+        <v>1.76</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="G7" t="n">
-        <v>2.98</v>
+        <v>2.54</v>
       </c>
       <c r="H7" t="n">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="J7" t="n">
         <v>3.1</v>
@@ -1748,7 +1748,7 @@
         <v>1.5</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
         <v>3.1</v>
@@ -1757,28 +1757,28 @@
         <v>1.42</v>
       </c>
       <c r="P7" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R7" t="n">
         <v>1.26</v>
       </c>
       <c r="S7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T7" t="n">
         <v>1.89</v>
       </c>
       <c r="U7" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="V7" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="X7" t="n">
         <v>19.5</v>
@@ -1829,25 +1829,25 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
         <v>500</v>
       </c>
       <c r="AP7" t="n">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR7" t="n">
         <v>9</v>
       </c>
       <c r="AS7" t="n">
-        <v>9</v>
+        <v>4.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AU7" t="n">
         <v>6.4</v>
@@ -1856,7 +1856,7 @@
         <v>7.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX7" t="n">
         <v>7.6</v>
@@ -1865,32 +1865,32 @@
         <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>40</v>
+        <v>4.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J8" t="n">
         <v>3.2</v>
@@ -1969,22 +1969,22 @@
         <v>1.63</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="n">
         <v>13</v>
       </c>
       <c r="Z8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA8" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB8" t="n">
         <v>6</v>
@@ -1993,7 +1993,7 @@
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
@@ -2008,13 +2008,13 @@
         <v>32</v>
       </c>
       <c r="AI8" t="n">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="AJ8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AL8" t="n">
         <v>1000</v>
@@ -2023,7 +2023,7 @@
         <v>300</v>
       </c>
       <c r="AN8" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AO8" t="n">
         <v>240</v>
@@ -2032,10 +2032,10 @@
         <v>7.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS8" t="n">
         <v>42</v>
@@ -2059,32 +2059,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB8" t="n">
         <v>20</v>
       </c>
       <c r="BC8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BD8" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BE8" t="n">
         <v>50</v>
       </c>
       <c r="BF8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG8" t="n">
         <v>46</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G9" t="n">
         <v>1.74</v>
@@ -2124,43 +2124,43 @@
         <v>6.8</v>
       </c>
       <c r="I9" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9" t="n">
         <v>3.45</v>
       </c>
       <c r="K9" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M9" t="n">
         <v>1.11</v>
       </c>
       <c r="N9" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="O9" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="P9" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="R9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S9" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="U9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V9" t="n">
         <v>1.16</v>
@@ -2169,7 +2169,7 @@
         <v>2.34</v>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y9" t="n">
         <v>18</v>
@@ -2184,10 +2184,10 @@
         <v>6.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
@@ -2199,7 +2199,7 @@
         <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
@@ -2208,7 +2208,7 @@
         <v>18</v>
       </c>
       <c r="AK9" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AL9" t="n">
         <v>1000</v>
@@ -2217,7 +2217,7 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
@@ -2229,13 +2229,13 @@
         <v>14</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AU9" t="n">
         <v>7.2</v>
@@ -2253,7 +2253,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BA9" t="n">
         <v>8.6</v>
@@ -2265,7 +2265,7 @@
         <v>17.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="BE9" t="n">
         <v>8.800000000000001</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G2" t="n">
         <v>1.73</v>
       </c>
-      <c r="G2" t="n">
-        <v>1.79</v>
-      </c>
       <c r="H2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="J2" t="n">
         <v>3.8</v>
@@ -775,40 +775,40 @@
         <v>3.95</v>
       </c>
       <c r="L2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
         <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P2" t="n">
         <v>1.68</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R2" t="n">
         <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U2" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W2" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="X2" t="n">
         <v>11</v>
@@ -817,10 +817,10 @@
         <v>16</v>
       </c>
       <c r="Z2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AA2" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB2" t="n">
         <v>6.6</v>
@@ -832,10 +832,10 @@
         <v>25</v>
       </c>
       <c r="AE2" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="AF2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG2" t="n">
         <v>10.5</v>
@@ -847,7 +847,7 @@
         <v>240</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK2" t="n">
         <v>22</v>
@@ -859,22 +859,22 @@
         <v>210</v>
       </c>
       <c r="AN2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>190</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS2" t="n">
         <v>16</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>16.5</v>
       </c>
       <c r="AT2" t="n">
         <v>6</v>
@@ -886,10 +886,10 @@
         <v>21</v>
       </c>
       <c r="AW2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY2" t="n">
         <v>9.4</v>
@@ -898,29 +898,29 @@
         <v>24</v>
       </c>
       <c r="BA2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BB2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC2" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE2" t="n">
-        <v>16.5</v>
+        <v>65</v>
       </c>
       <c r="BF2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="G3" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="H3" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="I3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J3" t="n">
         <v>3</v>
@@ -972,19 +972,19 @@
         <v>1.55</v>
       </c>
       <c r="M3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="n">
         <v>2.84</v>
       </c>
       <c r="O3" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="R3" t="n">
         <v>1.22</v>
@@ -993,7 +993,7 @@
         <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
         <v>1.9</v>
@@ -1002,70 +1002,70 @@
         <v>1.47</v>
       </c>
       <c r="W3" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X3" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Z3" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="AA3" t="n">
-        <v>130</v>
+        <v>340</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AG3" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH3" t="n">
         <v>55</v>
       </c>
       <c r="AI3" t="n">
-        <v>500</v>
+        <v>380</v>
       </c>
       <c r="AJ3" t="n">
-        <v>55</v>
+        <v>280</v>
       </c>
       <c r="AK3" t="n">
         <v>100</v>
       </c>
       <c r="AL3" t="n">
-        <v>380</v>
+        <v>150</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AS3" t="n">
         <v>20</v>
@@ -1074,47 +1074,47 @@
         <v>7.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV3" t="n">
         <v>12</v>
       </c>
       <c r="AW3" t="n">
-        <v>34</v>
+        <v>18.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.6</v>
+        <v>15.5</v>
       </c>
       <c r="AY3" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC3" t="n">
         <v>18.5</v>
       </c>
-      <c r="BA3" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>36</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>16</v>
-      </c>
       <c r="BD3" t="n">
-        <v>9.6</v>
+        <v>38</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -1145,121 +1145,121 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="G4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L4" t="n">
         <v>1.39</v>
       </c>
-      <c r="H4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="M4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X4" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>770</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC4" t="n">
         <v>13</v>
       </c>
-      <c r="J4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X4" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>760</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="AD4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>320</v>
+      </c>
+      <c r="AF4" t="n">
         <v>7.4</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>280</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>7.8</v>
       </c>
       <c r="AG4" t="n">
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AJ4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AK4" t="n">
         <v>16.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AR4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS4" t="n">
         <v>11</v>
@@ -1268,47 +1268,47 @@
         <v>6.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV4" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AW4" t="n">
         <v>10.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY4" t="n">
         <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BA4" t="n">
         <v>10.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC4" t="n">
         <v>14.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BE4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BG4" t="n">
         <v>15</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="G5" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J5" t="n">
         <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>1.55</v>
@@ -1363,55 +1363,55 @@
         <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O5" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S5" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="V5" t="n">
         <v>1.15</v>
       </c>
       <c r="W5" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="X5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Y5" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z5" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
@@ -1423,7 +1423,7 @@
         <v>11.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR5" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AS5" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AW5" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX5" t="n">
         <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BC5" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE5" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="G6" t="n">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="H6" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="J6" t="n">
         <v>3.05</v>
@@ -1554,37 +1554,37 @@
         <v>1.52</v>
       </c>
       <c r="M6" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P6" t="n">
         <v>1.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="U6" t="n">
         <v>1.94</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="X6" t="n">
         <v>17.5</v>
@@ -1602,7 +1602,7 @@
         <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1623,7 +1623,7 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
         <v>1000</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="AR6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>2.34</v>
       </c>
-      <c r="AS6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>3.45</v>
-      </c>
       <c r="BA6" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.4</v>
+        <v>2.12</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.76</v>
+        <v>2.08</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
         <v>3.3</v>
       </c>
       <c r="I7" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J7" t="n">
         <v>3.1</v>
@@ -1745,16 +1745,16 @@
         <v>3.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
         <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P7" t="n">
         <v>1.7</v>
@@ -1775,7 +1775,7 @@
         <v>1.92</v>
       </c>
       <c r="V7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W7" t="n">
         <v>1.64</v>
@@ -1790,28 +1790,28 @@
         <v>500</v>
       </c>
       <c r="AA7" t="n">
-        <v>900</v>
+        <v>230</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AC7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD7" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AE7" t="n">
         <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG7" t="n">
         <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AI7" t="n">
         <v>500</v>
@@ -1835,62 +1835,62 @@
         <v>500</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="AR7" t="n">
         <v>9</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.4</v>
+        <v>9.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="AU7" t="n">
         <v>6.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AY7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG7" t="n">
         <v>9</v>
       </c>
-      <c r="BD7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>8</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="G8" t="n">
         <v>2.02</v>
@@ -1933,10 +1933,10 @@
         <v>5.3</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L8" t="n">
         <v>1.64</v>
@@ -1951,10 +1951,10 @@
         <v>1.62</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="R8" t="n">
         <v>1.17</v>
@@ -1963,10 +1963,10 @@
         <v>6.4</v>
       </c>
       <c r="T8" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U8" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V8" t="n">
         <v>1.23</v>
@@ -1978,22 +1978,22 @@
         <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z8" t="n">
         <v>38</v>
       </c>
       <c r="AA8" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
         <v>6</v>
       </c>
       <c r="AC8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
@@ -2008,25 +2008,25 @@
         <v>32</v>
       </c>
       <c r="AI8" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
         <v>26</v>
       </c>
       <c r="AK8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AL8" t="n">
         <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AN8" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AO8" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
         <v>7.2</v>
@@ -2035,7 +2035,7 @@
         <v>10.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AS8" t="n">
         <v>42</v>
@@ -2044,25 +2044,25 @@
         <v>5.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AW8" t="n">
         <v>38</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA8" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="BB8" t="n">
         <v>20</v>
@@ -2071,10 +2071,10 @@
         <v>26</v>
       </c>
       <c r="BD8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE8" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="BF8" t="n">
         <v>22</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -2115,40 +2115,40 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G9" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H9" t="n">
         <v>6.8</v>
       </c>
       <c r="I9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L9" t="n">
         <v>1.55</v>
       </c>
       <c r="M9" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N9" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P9" t="n">
         <v>1.57</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="R9" t="n">
         <v>1.2</v>
@@ -2157,10 +2157,10 @@
         <v>5.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V9" t="n">
         <v>1.16</v>
@@ -2169,7 +2169,7 @@
         <v>2.34</v>
       </c>
       <c r="X9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="n">
         <v>18</v>
@@ -2184,10 +2184,10 @@
         <v>6.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
@@ -2196,7 +2196,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH9" t="n">
         <v>1000</v>
@@ -2208,7 +2208,7 @@
         <v>18</v>
       </c>
       <c r="AK9" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AL9" t="n">
         <v>1000</v>
@@ -2217,68 +2217,68 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV9" t="n">
         <v>7.8</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>21</v>
-      </c>
       <c r="AW9" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ9" t="n">
         <v>8</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB9" t="n">
         <v>13</v>
       </c>
       <c r="BC9" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>42</v>
+        <v>7.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -757,58 +757,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="G2" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="H2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I2" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M2" t="n">
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P2" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="Q2" t="n">
         <v>2.38</v>
       </c>
       <c r="R2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
         <v>4.7</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V2" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W2" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="X2" t="n">
         <v>11</v>
@@ -817,25 +817,25 @@
         <v>16</v>
       </c>
       <c r="Z2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA2" t="n">
-        <v>210</v>
+        <v>900</v>
       </c>
       <c r="AB2" t="n">
         <v>6.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG2" t="n">
         <v>10.5</v>
@@ -847,7 +847,7 @@
         <v>240</v>
       </c>
       <c r="AJ2" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AK2" t="n">
         <v>22</v>
@@ -859,7 +859,7 @@
         <v>210</v>
       </c>
       <c r="AN2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO2" t="n">
         <v>190</v>
@@ -889,7 +889,7 @@
         <v>15</v>
       </c>
       <c r="AX2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY2" t="n">
         <v>9.4</v>
@@ -898,29 +898,29 @@
         <v>24</v>
       </c>
       <c r="BA2" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="BB2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BE2" t="n">
-        <v>65</v>
+        <v>16.5</v>
       </c>
       <c r="BF2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG2" t="n">
         <v>14</v>
       </c>
-      <c r="BG2" t="n">
-        <v>16</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
         <v>2.98</v>
       </c>
       <c r="H3" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I3" t="n">
         <v>3.1</v>
@@ -966,10 +966,10 @@
         <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M3" t="n">
         <v>1.11</v>
@@ -978,76 +978,76 @@
         <v>2.84</v>
       </c>
       <c r="O3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P3" t="n">
         <v>1.61</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="R3" t="n">
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
         <v>1.9</v>
       </c>
       <c r="V3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W3" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Z3" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="AA3" t="n">
-        <v>340</v>
+        <v>130</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC3" t="n">
         <v>7.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF3" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AG3" t="n">
         <v>13.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AI3" t="n">
         <v>380</v>
       </c>
       <c r="AJ3" t="n">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="AK3" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AL3" t="n">
-        <v>150</v>
+        <v>380</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1056,22 +1056,22 @@
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP3" t="n">
         <v>8.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AS3" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU3" t="n">
         <v>6.4</v>
@@ -1080,41 +1080,41 @@
         <v>12</v>
       </c>
       <c r="AW3" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AX3" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AY3" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="BB3" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="BD3" t="n">
         <v>38</v>
       </c>
       <c r="BE3" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="BF3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG3" t="n">
         <v>11.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -1148,19 +1148,19 @@
         <v>1.33</v>
       </c>
       <c r="G4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="I4" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="J4" t="n">
         <v>5.4</v>
       </c>
       <c r="K4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L4" t="n">
         <v>1.39</v>
@@ -1175,52 +1175,52 @@
         <v>1.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R4" t="n">
         <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T4" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U4" t="n">
         <v>1.64</v>
       </c>
       <c r="V4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W4" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="X4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Z4" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>770</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
         <v>7.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD4" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AE4" t="n">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="AF4" t="n">
         <v>7.4</v>
@@ -1232,19 +1232,19 @@
         <v>40</v>
       </c>
       <c r="AI4" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AJ4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AK4" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AN4" t="n">
         <v>7</v>
@@ -1256,10 +1256,10 @@
         <v>15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AR4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS4" t="n">
         <v>11</v>
@@ -1268,10 +1268,10 @@
         <v>6.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AW4" t="n">
         <v>10.5</v>
@@ -1283,32 +1283,32 @@
         <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BA4" t="n">
         <v>10.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD4" t="n">
         <v>40</v>
       </c>
       <c r="BE4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BG4" t="n">
         <v>15</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
         <v>1.55</v>
@@ -1363,7 +1363,7 @@
         <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O5" t="n">
         <v>1.5</v>
@@ -1372,7 +1372,7 @@
         <v>1.61</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R5" t="n">
         <v>1.21</v>
@@ -1381,31 +1381,31 @@
         <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="U5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V5" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="X5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y5" t="n">
         <v>19</v>
       </c>
       <c r="Z5" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AC5" t="n">
         <v>8.800000000000001</v>
@@ -1417,7 +1417,7 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG5" t="n">
         <v>11.5</v>
@@ -1450,13 +1450,13 @@
         <v>8.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT5" t="n">
         <v>5.2</v>
@@ -1465,22 +1465,22 @@
         <v>7.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AW5" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AX5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY5" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB5" t="n">
         <v>14</v>
@@ -1489,20 +1489,20 @@
         <v>19</v>
       </c>
       <c r="BD5" t="n">
-        <v>9.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF5" t="n">
         <v>13.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -1536,13 +1536,13 @@
         <v>2.46</v>
       </c>
       <c r="G6" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H6" t="n">
         <v>3.3</v>
       </c>
       <c r="I6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J6" t="n">
         <v>3.05</v>
@@ -1563,16 +1563,16 @@
         <v>1.45</v>
       </c>
       <c r="P6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="R6" t="n">
         <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T6" t="n">
         <v>1.94</v>
@@ -1581,7 +1581,7 @@
         <v>1.94</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
         <v>1.61</v>
@@ -1596,107 +1596,107 @@
         <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>380</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA6" t="n">
         <v>42</v>
       </c>
-      <c r="AD6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>2.08</v>
-      </c>
       <c r="BB6" t="n">
-        <v>2.12</v>
+        <v>8.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.56</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD6" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.1</v>
+        <v>7.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.02</v>
+        <v>3.1</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.08</v>
+        <v>2.48</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -1727,73 +1727,73 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="G7" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="H7" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I7" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L7" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P7" t="n">
         <v>1.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R7" t="n">
         <v>1.26</v>
       </c>
       <c r="S7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="U7" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V7" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X7" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="Z7" t="n">
         <v>500</v>
       </c>
       <c r="AA7" t="n">
-        <v>230</v>
+        <v>160</v>
       </c>
       <c r="AB7" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AC7" t="n">
         <v>13</v>
@@ -1832,25 +1832,25 @@
         <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.9</v>
+        <v>9.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AR7" t="n">
         <v>9</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AV7" t="n">
         <v>7.8</v>
@@ -1859,38 +1859,38 @@
         <v>9</v>
       </c>
       <c r="AX7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AY7" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
         <v>11.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.6</v>
+        <v>30</v>
       </c>
       <c r="BC7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG7" t="n">
         <v>8</v>
       </c>
-      <c r="BG7" t="n">
-        <v>9</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -1927,13 +1927,13 @@
         <v>2.02</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
         <v>3.3</v>
@@ -1945,19 +1945,19 @@
         <v>1.14</v>
       </c>
       <c r="N8" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O8" t="n">
         <v>1.62</v>
       </c>
       <c r="P8" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="R8" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S8" t="n">
         <v>6.4</v>
@@ -1966,10 +1966,10 @@
         <v>2.4</v>
       </c>
       <c r="U8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
         <v>1.98</v>
@@ -1981,19 +1981,19 @@
         <v>12.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
@@ -2005,40 +2005,40 @@
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AM8" t="n">
-        <v>290</v>
+        <v>360</v>
       </c>
       <c r="AN8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AP8" t="n">
         <v>7.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AS8" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AT8" t="n">
         <v>5.5</v>
@@ -2050,10 +2050,10 @@
         <v>19.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY8" t="n">
         <v>10</v>
@@ -2062,29 +2062,29 @@
         <v>25</v>
       </c>
       <c r="BA8" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BB8" t="n">
         <v>20</v>
       </c>
       <c r="BC8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD8" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BE8" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="BF8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BG8" t="n">
         <v>46</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -2124,13 +2124,13 @@
         <v>6.8</v>
       </c>
       <c r="I9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.55</v>
@@ -2145,28 +2145,28 @@
         <v>1.51</v>
       </c>
       <c r="P9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q9" t="n">
         <v>2.56</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S9" t="n">
         <v>5.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="U9" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V9" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W9" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X9" t="n">
         <v>11</v>
@@ -2175,7 +2175,7 @@
         <v>18</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
@@ -2193,7 +2193,7 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG9" t="n">
         <v>11.5</v>
@@ -2211,7 +2211,7 @@
         <v>26</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
@@ -2223,40 +2223,40 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ9" t="n">
         <v>13</v>
       </c>
       <c r="AR9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU9" t="n">
         <v>7.2</v>
       </c>
-      <c r="AS9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AV9" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB9" t="n">
         <v>13</v>
@@ -2265,20 +2265,20 @@
         <v>18.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BF9" t="n">
         <v>13</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -760,10 +760,10 @@
         <v>1.73</v>
       </c>
       <c r="G2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="H2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I2" t="n">
         <v>6.2</v>
@@ -790,7 +790,7 @@
         <v>1.71</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="R2" t="n">
         <v>1.25</v>
@@ -799,82 +799,82 @@
         <v>4.7</v>
       </c>
       <c r="T2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U2" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V2" t="n">
         <v>1.19</v>
       </c>
       <c r="W2" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="X2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z2" t="n">
         <v>46</v>
       </c>
       <c r="AA2" t="n">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="AB2" t="n">
         <v>6.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
         <v>24</v>
       </c>
       <c r="AE2" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AF2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AH2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI2" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK2" t="n">
         <v>22</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM2" t="n">
-        <v>210</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
         <v>16</v>
       </c>
       <c r="AO2" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AS2" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AT2" t="n">
         <v>6</v>
@@ -886,19 +886,19 @@
         <v>21</v>
       </c>
       <c r="AW2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
         <v>24</v>
       </c>
       <c r="BA2" t="n">
-        <v>65</v>
+        <v>16.5</v>
       </c>
       <c r="BB2" t="n">
         <v>16.5</v>
@@ -907,20 +907,20 @@
         <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="BE2" t="n">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="BF2" t="n">
         <v>14.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G3" t="n">
         <v>2.98</v>
@@ -960,13 +960,13 @@
         <v>2.94</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L3" t="n">
         <v>1.56</v>
@@ -975,40 +975,40 @@
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="P3" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S3" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="T3" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="U3" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V3" t="n">
         <v>1.48</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X3" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Z3" t="n">
         <v>24</v>
@@ -1017,7 +1017,7 @@
         <v>130</v>
       </c>
       <c r="AB3" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AC3" t="n">
         <v>7.2</v>
@@ -1026,7 +1026,7 @@
         <v>13.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>100</v>
+        <v>240</v>
       </c>
       <c r="AF3" t="n">
         <v>25</v>
@@ -1047,7 +1047,7 @@
         <v>110</v>
       </c>
       <c r="AL3" t="n">
-        <v>380</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1056,28 +1056,28 @@
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>8.4</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>8</v>
       </c>
       <c r="AR3" t="n">
         <v>16</v>
       </c>
       <c r="AS3" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AT3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU3" t="n">
         <v>6.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW3" t="n">
         <v>20</v>
@@ -1089,10 +1089,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BB3" t="n">
         <v>19.5</v>
@@ -1101,20 +1101,20 @@
         <v>25</v>
       </c>
       <c r="BD3" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BE3" t="n">
         <v>28</v>
       </c>
       <c r="BF3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="G4" t="n">
         <v>1.38</v>
@@ -1154,10 +1154,10 @@
         <v>10.5</v>
       </c>
       <c r="I4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="J4" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K4" t="n">
         <v>6.2</v>
@@ -1187,10 +1187,10 @@
         <v>3.35</v>
       </c>
       <c r="T4" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="U4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V4" t="n">
         <v>1.08</v>
@@ -1223,7 +1223,7 @@
         <v>340</v>
       </c>
       <c r="AF4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AG4" t="n">
         <v>11</v>
@@ -1238,19 +1238,19 @@
         <v>11</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL4" t="n">
         <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="AN4" t="n">
         <v>7</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AP4" t="n">
         <v>15</v>
@@ -1259,7 +1259,7 @@
         <v>25</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="AS4" t="n">
         <v>11</v>
@@ -1271,19 +1271,19 @@
         <v>11.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AW4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BA4" t="n">
         <v>10.5</v>
@@ -1295,10 +1295,10 @@
         <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BE4" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="BF4" t="n">
         <v>6</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>1.62</v>
       </c>
       <c r="G5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="H5" t="n">
         <v>7.4</v>
@@ -1381,10 +1381,10 @@
         <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>1.13</v>
@@ -1399,7 +1399,7 @@
         <v>19</v>
       </c>
       <c r="Z5" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
@@ -1432,10 +1432,10 @@
         <v>17.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
@@ -1450,13 +1450,13 @@
         <v>8.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR5" t="n">
         <v>38</v>
       </c>
       <c r="AS5" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="AT5" t="n">
         <v>5.2</v>
@@ -1480,7 +1480,7 @@
         <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB5" t="n">
         <v>14</v>
@@ -1489,20 +1489,20 @@
         <v>19</v>
       </c>
       <c r="BD5" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BE5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF5" t="n">
         <v>13.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G6" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="H6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K6" t="n">
         <v>3.3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.35</v>
       </c>
       <c r="L6" t="n">
         <v>1.52</v>
@@ -1557,49 +1557,49 @@
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P6" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
         <v>4.5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="U6" t="n">
         <v>1.94</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="X6" t="n">
         <v>17.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="AC6" t="n">
         <v>14</v>
@@ -1608,7 +1608,7 @@
         <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>500</v>
+        <v>270</v>
       </c>
       <c r="AF6" t="n">
         <v>1000</v>
@@ -1623,7 +1623,7 @@
         <v>380</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
         <v>1000</v>
@@ -1641,16 +1641,16 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.15</v>
+        <v>8.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="AT6" t="n">
         <v>5.4</v>
@@ -1662,7 +1662,7 @@
         <v>7</v>
       </c>
       <c r="AW6" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="AX6" t="n">
         <v>8</v>
@@ -1671,32 +1671,32 @@
         <v>7.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA6" t="n">
-        <v>42</v>
+        <v>10.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BD6" t="n">
         <v>36</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.1</v>
+        <v>32</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.48</v>
+        <v>3.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -1733,10 +1733,10 @@
         <v>2.58</v>
       </c>
       <c r="H7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I7" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J7" t="n">
         <v>3.2</v>
@@ -1757,46 +1757,46 @@
         <v>1.42</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R7" t="n">
         <v>1.26</v>
       </c>
       <c r="S7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U7" t="n">
         <v>1.92</v>
       </c>
-      <c r="U7" t="n">
-        <v>1.9</v>
-      </c>
       <c r="V7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
         <v>1.63</v>
       </c>
       <c r="X7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y7" t="n">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="Z7" t="n">
         <v>500</v>
       </c>
       <c r="AA7" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AC7" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="AD7" t="n">
         <v>500</v>
@@ -1811,7 +1811,7 @@
         <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI7" t="n">
         <v>500</v>
@@ -1835,7 +1835,7 @@
         <v>600</v>
       </c>
       <c r="AP7" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ7" t="n">
         <v>7</v>
@@ -1844,10 +1844,10 @@
         <v>9</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.6</v>
+        <v>20</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="AU7" t="n">
         <v>6</v>
@@ -1856,41 +1856,41 @@
         <v>7.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AX7" t="n">
         <v>11</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
         <v>11.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BB7" t="n">
         <v>30</v>
       </c>
       <c r="BC7" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.4</v>
+        <v>23</v>
       </c>
       <c r="BE7" t="n">
         <v>10.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>1.99</v>
       </c>
       <c r="G8" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H8" t="n">
         <v>5.1</v>
@@ -1945,16 +1945,16 @@
         <v>1.14</v>
       </c>
       <c r="N8" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O8" t="n">
         <v>1.62</v>
       </c>
       <c r="P8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="R8" t="n">
         <v>1.16</v>
@@ -1969,10 +1969,10 @@
         <v>1.65</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W8" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X8" t="n">
         <v>8</v>
@@ -1981,19 +1981,19 @@
         <v>12.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA8" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
@@ -2002,7 +2002,7 @@
         <v>10</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
         <v>34</v>
@@ -2014,7 +2014,7 @@
         <v>25</v>
       </c>
       <c r="AK8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AL8" t="n">
         <v>990</v>
@@ -2023,22 +2023,22 @@
         <v>360</v>
       </c>
       <c r="AN8" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AO8" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
         <v>7.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AS8" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AT8" t="n">
         <v>5.5</v>
@@ -2050,7 +2050,7 @@
         <v>19.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AX8" t="n">
         <v>9</v>
@@ -2059,7 +2059,7 @@
         <v>10</v>
       </c>
       <c r="AZ8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA8" t="n">
         <v>75</v>
@@ -2071,20 +2071,20 @@
         <v>25</v>
       </c>
       <c r="BD8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE8" t="n">
         <v>50</v>
       </c>
       <c r="BF8" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="BG8" t="n">
         <v>46</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G9" t="n">
         <v>1.73</v>
@@ -2127,7 +2127,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
         <v>3.8</v>
@@ -2151,7 +2151,7 @@
         <v>2.56</v>
       </c>
       <c r="R9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S9" t="n">
         <v>5.3</v>
@@ -2160,22 +2160,22 @@
         <v>2.34</v>
       </c>
       <c r="U9" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="V9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W9" t="n">
         <v>2.36</v>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
@@ -2193,7 +2193,7 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG9" t="n">
         <v>11.5</v>
@@ -2205,13 +2205,13 @@
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AK9" t="n">
         <v>26</v>
       </c>
       <c r="AL9" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
@@ -2223,16 +2223,16 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ9" t="n">
         <v>13</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT9" t="n">
         <v>5.2</v>
@@ -2241,44 +2241,44 @@
         <v>7.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB9" t="n">
         <v>13</v>
       </c>
       <c r="BC9" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF9" t="n">
         <v>13</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="G2" t="n">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="H2" t="n">
-        <v>5.9</v>
+        <v>28</v>
       </c>
       <c r="I2" t="n">
+        <v>32</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" t="n">
         <v>6.2</v>
       </c>
-      <c r="J2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.9</v>
-      </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P2" t="n">
         <v>1.51</v>
       </c>
-      <c r="M2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.71</v>
-      </c>
       <c r="Q2" t="n">
-        <v>2.34</v>
+        <v>2.82</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="T2" t="n">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="U2" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="V2" t="n">
-        <v>1.19</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>2.28</v>
+        <v>5</v>
       </c>
       <c r="X2" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.6</v>
+        <v>3.55</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="AE2" t="n">
-        <v>240</v>
+        <v>400</v>
       </c>
       <c r="AF2" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AH2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>440</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK2" t="n">
         <v>27</v>
       </c>
-      <c r="AI2" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>22</v>
-      </c>
       <c r="AL2" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="AM2" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="AO2" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="AR2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV2" t="n">
         <v>34</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>21</v>
       </c>
       <c r="AW2" t="n">
         <v>16</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AZ2" t="n">
+        <v>38</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>300</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>410</v>
+      </c>
+      <c r="BF2" t="n">
         <v>24</v>
       </c>
-      <c r="BA2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BG2" t="n">
-        <v>17</v>
+        <v>280</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
@@ -951,52 +951,52 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G3" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H3" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="I3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
         <v>3.15</v>
       </c>
       <c r="L3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="M3" t="n">
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="O3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P3" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="R3" t="n">
         <v>1.23</v>
       </c>
       <c r="S3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V3" t="n">
         <v>1.48</v>
@@ -1005,70 +1005,70 @@
         <v>1.51</v>
       </c>
       <c r="X3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y3" t="n">
         <v>9.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD3" t="n">
         <v>13.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="AF3" t="n">
-        <v>25</v>
+        <v>17.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
         <v>40</v>
       </c>
       <c r="AI3" t="n">
-        <v>380</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="AK3" t="n">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="AL3" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO3" t="n">
-        <v>600</v>
+        <v>50</v>
       </c>
       <c r="AP3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR3" t="n">
         <v>16</v>
       </c>
       <c r="AS3" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AT3" t="n">
         <v>8.199999999999999</v>
@@ -1077,16 +1077,16 @@
         <v>6.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AX3" t="n">
         <v>12</v>
       </c>
       <c r="AY3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>17.5</v>
@@ -1098,23 +1098,23 @@
         <v>19.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD3" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="BE3" t="n">
         <v>28</v>
       </c>
       <c r="BF3" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="BG3" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="G4" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="H4" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="J4" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
         <v>3.9</v>
@@ -1175,7 +1175,7 @@
         <v>1.3</v>
       </c>
       <c r="P4" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
         <v>1.9</v>
@@ -1184,73 +1184,73 @@
         <v>1.38</v>
       </c>
       <c r="S4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W4" t="n">
         <v>3.35</v>
       </c>
-      <c r="T4" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3.6</v>
-      </c>
       <c r="X4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y4" t="n">
         <v>32</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>560</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AD4" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AE4" t="n">
         <v>340</v>
       </c>
       <c r="AF4" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AI4" t="n">
         <v>300</v>
       </c>
       <c r="AJ4" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM4" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AO4" t="n">
-        <v>490</v>
+        <v>320</v>
       </c>
       <c r="AP4" t="n">
         <v>15</v>
@@ -1259,56 +1259,56 @@
         <v>25</v>
       </c>
       <c r="AR4" t="n">
-        <v>30</v>
+        <v>9.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT4" t="n">
         <v>6.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AW4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AY4" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BC4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BE4" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="BF4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BG4" t="n">
         <v>15</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
@@ -1339,34 +1339,34 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="H5" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="L5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M5" t="n">
         <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P5" t="n">
         <v>1.61</v>
@@ -1375,73 +1375,73 @@
         <v>2.48</v>
       </c>
       <c r="R5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V5" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="X5" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Y5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>19</v>
       </c>
-      <c r="Z5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
@@ -1450,28 +1450,28 @@
         <v>8.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR5" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AS5" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AY5" t="n">
         <v>9.4</v>
@@ -1480,29 +1480,29 @@
         <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB5" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BC5" t="n">
         <v>19</v>
       </c>
       <c r="BD5" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="BE5" t="n">
         <v>11</v>
       </c>
       <c r="BF5" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BG5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
@@ -1533,127 +1533,127 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="G6" t="n">
-        <v>2.72</v>
+        <v>2.42</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="I6" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="J6" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="L6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P6" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S6" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="T6" t="n">
         <v>1.9</v>
       </c>
       <c r="U6" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="X6" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>270</v>
       </c>
       <c r="AB6" t="n">
         <v>46</v>
       </c>
       <c r="AC6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE6" t="n">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG6" t="n">
         <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI6" t="n">
         <v>380</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>6.6</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AR6" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS6" t="n">
         <v>44</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU6" t="n">
         <v>5</v>
@@ -1662,41 +1662,41 @@
         <v>7</v>
       </c>
       <c r="AW6" t="n">
-        <v>20</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="AZ6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BA6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG6" t="n">
         <v>10.5</v>
       </c>
-      <c r="BB6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>32</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>3.2</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
@@ -1727,49 +1727,49 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G7" t="n">
         <v>2.58</v>
       </c>
       <c r="H7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I7" t="n">
         <v>3.5</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L7" t="n">
         <v>1.5</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
         <v>3.15</v>
       </c>
       <c r="O7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P7" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R7" t="n">
         <v>1.26</v>
       </c>
       <c r="S7" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U7" t="n">
         <v>1.92</v>
@@ -1781,10 +1781,10 @@
         <v>1.63</v>
       </c>
       <c r="X7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y7" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Z7" t="n">
         <v>500</v>
@@ -1793,25 +1793,25 @@
         <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>29</v>
+        <v>15.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AE7" t="n">
         <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH7" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI7" t="n">
         <v>500</v>
@@ -1829,7 +1829,7 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO7" t="n">
         <v>600</v>
@@ -1844,10 +1844,10 @@
         <v>9</v>
       </c>
       <c r="AS7" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AU7" t="n">
         <v>6</v>
@@ -1856,7 +1856,7 @@
         <v>7.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AX7" t="n">
         <v>11</v>
@@ -1874,23 +1874,23 @@
         <v>30</v>
       </c>
       <c r="BC7" t="n">
-        <v>14.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD7" t="n">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="BE7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BG7" t="n">
         <v>10.5</v>
       </c>
-      <c r="BF7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
@@ -1921,31 +1921,31 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="G8" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H8" t="n">
         <v>5.1</v>
       </c>
       <c r="I8" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L8" t="n">
         <v>1.64</v>
       </c>
       <c r="M8" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N8" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="O8" t="n">
         <v>1.62</v>
@@ -1954,137 +1954,137 @@
         <v>1.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="R8" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="T8" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U8" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V8" t="n">
         <v>1.23</v>
       </c>
       <c r="W8" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X8" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="Y8" t="n">
         <v>12.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF8" t="n">
         <v>10</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
         <v>34</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK8" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AL8" t="n">
-        <v>990</v>
+        <v>75</v>
       </c>
       <c r="AM8" t="n">
-        <v>360</v>
+        <v>280</v>
       </c>
       <c r="AN8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AP8" t="n">
         <v>7.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AS8" t="n">
         <v>42</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW8" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AX8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA8" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="BB8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BD8" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BE8" t="n">
         <v>50</v>
       </c>
       <c r="BF8" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BG8" t="n">
         <v>46</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
@@ -2115,25 +2115,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G9" t="n">
         <v>1.73</v>
       </c>
       <c r="H9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
         <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M9" t="n">
         <v>1.12</v>
@@ -2160,7 +2160,7 @@
         <v>2.34</v>
       </c>
       <c r="U9" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V9" t="n">
         <v>1.15</v>
@@ -2169,7 +2169,7 @@
         <v>2.36</v>
       </c>
       <c r="X9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="n">
         <v>17.5</v>
@@ -2184,10 +2184,10 @@
         <v>6.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
@@ -2199,52 +2199,52 @@
         <v>11.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AK9" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR9" t="n">
         <v>8</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AS9" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU9" t="n">
         <v>7.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX9" t="n">
         <v>7.4</v>
@@ -2253,32 +2253,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BC9" t="n">
         <v>20</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.6</v>
+        <v>21</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH9"/>
+  <dimension ref="A1:BH8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Racing Club (Uru)</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Progreso</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.24</v>
+        <v>2.7</v>
       </c>
       <c r="G2" t="n">
-        <v>1.25</v>
+        <v>2.8</v>
       </c>
       <c r="H2" t="n">
-        <v>28</v>
+        <v>3.05</v>
       </c>
       <c r="I2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>60</v>
+      </c>
+      <c r="BB2" t="n">
         <v>32</v>
       </c>
-      <c r="J2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W2" t="n">
-        <v>5</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD2" t="n">
+      <c r="BC2" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD2" t="n">
         <v>48</v>
       </c>
-      <c r="AE2" t="n">
-        <v>400</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>440</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>38</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>300</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>100</v>
-      </c>
       <c r="BE2" t="n">
-        <v>410</v>
+        <v>110</v>
       </c>
       <c r="BF2" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BG2" t="n">
-        <v>280</v>
+        <v>42</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,184 +937,184 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Real Santander</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.84</v>
+        <v>1.41</v>
       </c>
       <c r="G3" t="n">
-        <v>2.96</v>
+        <v>1.45</v>
       </c>
       <c r="H3" t="n">
-        <v>2.92</v>
+        <v>8.6</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1</v>
+        <v>10.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="K3" t="n">
-        <v>3.15</v>
+        <v>5.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="M3" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>2.92</v>
+        <v>3.85</v>
       </c>
       <c r="O3" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="P3" t="n">
-        <v>1.63</v>
+        <v>1.99</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.48</v>
+        <v>1.92</v>
       </c>
       <c r="R3" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="V3" t="n">
-        <v>1.48</v>
+        <v>1.1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.51</v>
+        <v>3.2</v>
       </c>
       <c r="X3" t="n">
-        <v>9.6</v>
+        <v>17.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.6</v>
+        <v>26</v>
       </c>
       <c r="Z3" t="n">
-        <v>18.5</v>
+        <v>90</v>
       </c>
       <c r="AA3" t="n">
-        <v>55</v>
+        <v>560</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AC3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>190</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>300</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>300</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX3" t="n">
         <v>7</v>
       </c>
-      <c r="AD3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO3" t="n">
+      <c r="AY3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>27</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE3" t="n">
         <v>50</v>
       </c>
-      <c r="AP3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>28</v>
-      </c>
       <c r="BF3" t="n">
-        <v>17</v>
+        <v>6.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -1131,184 +1131,184 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>Internacional de Palmira</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Real Santander</t>
+          <t>Tigres FC Zipaquira</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.39</v>
+        <v>1.74</v>
       </c>
       <c r="G4" t="n">
-        <v>1.42</v>
+        <v>1.81</v>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>11.5</v>
+        <v>6.8</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="O4" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.9</v>
+        <v>2.48</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="T4" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="U4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="W4" t="n">
-        <v>3.35</v>
+        <v>2.22</v>
       </c>
       <c r="X4" t="n">
-        <v>18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>32</v>
+        <v>16.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="AA4" t="n">
-        <v>560</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="AE4" t="n">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AI4" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AL4" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="AO4" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>15</v>
+        <v>8.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.6</v>
+        <v>27</v>
       </c>
       <c r="AS4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AW4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AY4" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB4" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="BD4" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BE4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="BG4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Internacional de Palmira</t>
+          <t>Independiente Yumbo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Boyaca Patriotas</t>
         </is>
       </c>
       <c r="F5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P5" t="n">
         <v>1.74</v>
       </c>
-      <c r="G5" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="H5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.61</v>
-      </c>
       <c r="Q5" t="n">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="R5" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.24</v>
+        <v>1.89</v>
       </c>
       <c r="U5" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>2.22</v>
+        <v>1.7</v>
       </c>
       <c r="X5" t="n">
-        <v>9.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>16.5</v>
+        <v>500</v>
       </c>
       <c r="Z5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
+        <v>270</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>270</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1000</v>
       </c>
-      <c r="AB5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE5" t="n">
+      <c r="AH5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>380</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL5" t="n">
         <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>100</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>18</v>
+        <v>600</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR5" t="n">
         <v>8.4</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>27</v>
-      </c>
       <c r="AS5" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="AV5" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="AW5" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AX5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.4</v>
+        <v>6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>20</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB5" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="BD5" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="BE5" t="n">
-        <v>11</v>
+        <v>2.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>15</v>
+        <v>8.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>11</v>
+        <v>4.1</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,186 +1524,186 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Independiente Yumbo</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Boyaca Patriotas</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H6" t="n">
         <v>3.55</v>
       </c>
       <c r="I6" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K6" t="n">
         <v>3.45</v>
       </c>
       <c r="L6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
         <v>1.43</v>
       </c>
       <c r="P6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R6" t="n">
         <v>1.26</v>
       </c>
       <c r="S6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U6" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
         <v>1.71</v>
       </c>
       <c r="X6" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y6" t="n">
         <v>21</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA6" t="n">
-        <v>270</v>
+        <v>160</v>
       </c>
       <c r="AB6" t="n">
-        <v>46</v>
+        <v>15.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AD6" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AE6" t="n">
         <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH6" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI6" t="n">
-        <v>380</v>
+        <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AK6" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AL6" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
         <v>600</v>
       </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP6" t="n">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AR6" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AS6" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>9.800000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AY6" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="BB6" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="BC6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BF6" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.44</v>
+        <v>2.02</v>
       </c>
       <c r="G7" t="n">
-        <v>2.58</v>
+        <v>2.06</v>
       </c>
       <c r="H7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J7" t="n">
         <v>3.15</v>
       </c>
-      <c r="I7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.1</v>
-      </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="N7" t="n">
-        <v>3.15</v>
+        <v>2.52</v>
       </c>
       <c r="O7" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.32</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="S7" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.92</v>
+        <v>2.42</v>
       </c>
       <c r="U7" t="n">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="V7" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="W7" t="n">
-        <v>1.63</v>
+        <v>1.94</v>
       </c>
       <c r="X7" t="n">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AA7" t="n">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AB7" t="n">
-        <v>15.5</v>
+        <v>6.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE7" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AF7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>190</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>210</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR7" t="n">
         <v>30</v>
       </c>
-      <c r="AG7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>170</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ7" t="n">
+      <c r="AS7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU7" t="n">
         <v>7</v>
       </c>
-      <c r="AR7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6</v>
-      </c>
       <c r="AV7" t="n">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="AW7" t="n">
-        <v>19.5</v>
+        <v>85</v>
       </c>
       <c r="AX7" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY7" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>11.5</v>
+        <v>26</v>
       </c>
       <c r="BA7" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="BB7" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="BC7" t="n">
-        <v>9.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="BD7" t="n">
-        <v>10.5</v>
+        <v>60</v>
       </c>
       <c r="BE7" t="n">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="BF7" t="n">
-        <v>9.4</v>
+        <v>24</v>
       </c>
       <c r="BG7" t="n">
-        <v>10.5</v>
+        <v>60</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,373 +1912,179 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>Quindio</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Orsomarso</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="G8" t="n">
-        <v>2.06</v>
+        <v>1.74</v>
       </c>
       <c r="H8" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="I8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S8" t="n">
         <v>5.3</v>
       </c>
-      <c r="J8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="T8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V8" t="n">
         <v>1.15</v>
       </c>
-      <c r="N8" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.23</v>
-      </c>
       <c r="W8" t="n">
-        <v>1.94</v>
+        <v>2.34</v>
       </c>
       <c r="X8" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
         <v>6.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="AE8" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AI8" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AK8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL8" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AM8" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>28</v>
+        <v>17.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU8" t="n">
         <v>7.2</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AV8" t="n">
         <v>11</v>
       </c>
-      <c r="AR8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV8" t="n">
+      <c r="AW8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC8" t="n">
         <v>20</v>
       </c>
-      <c r="AW8" t="n">
-        <v>85</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>27</v>
-      </c>
       <c r="BD8" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="BE8" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="BF8" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="BG8" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Colombian Primera B</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Quindio</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Orsomarso</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I9" t="n">
-        <v>8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="X9" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>48</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>50</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH8"/>
+  <dimension ref="A1:BH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,184 +743,184 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Real Santander</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.7</v>
+        <v>1.51</v>
       </c>
       <c r="G2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W2" t="n">
         <v>2.8</v>
       </c>
-      <c r="H2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.62</v>
-      </c>
       <c r="X2" t="n">
-        <v>9.4</v>
+        <v>15.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="AA2" t="n">
-        <v>75</v>
+        <v>320</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="AE2" t="n">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="AF2" t="n">
-        <v>16</v>
+        <v>8.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="AH2" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>75</v>
+        <v>140</v>
       </c>
       <c r="AJ2" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="AK2" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="AL2" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AM2" t="n">
         <v>190</v>
       </c>
       <c r="AN2" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="AO2" t="n">
-        <v>75</v>
+        <v>240</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="AQ2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>170</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>150</v>
+      </c>
+      <c r="BF2" t="n">
         <v>8.6</v>
       </c>
-      <c r="AR2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>29</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>48</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>110</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>32</v>
-      </c>
       <c r="BG2" t="n">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -937,184 +937,184 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>Internacional de Palmira</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Real Santander</t>
+          <t>Tigres FC Zipaquira</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.41</v>
+        <v>1.77</v>
       </c>
       <c r="G3" t="n">
-        <v>1.45</v>
+        <v>1.81</v>
       </c>
       <c r="H3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC3" t="n">
         <v>8.6</v>
       </c>
-      <c r="I3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>26</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>560</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AD3" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="AE3" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG3" t="n">
         <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI3" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AK3" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AL3" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>7.8</v>
+        <v>18</v>
       </c>
       <c r="AO3" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>14.5</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>25</v>
-      </c>
       <c r="AR3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS3" t="n">
         <v>11.5</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="AT3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW3" t="n">
         <v>12.5</v>
       </c>
-      <c r="AT3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>12</v>
-      </c>
       <c r="AX3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BA3" t="n">
-        <v>12.5</v>
+        <v>36</v>
       </c>
       <c r="BB3" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="BD3" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BE3" t="n">
         <v>50</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Internacional de Palmira</t>
+          <t>Independiente Yumbo</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Boyaca Patriotas</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P4" t="n">
         <v>1.74</v>
       </c>
-      <c r="G4" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="H4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W4" t="n">
         <v>1.61</v>
       </c>
-      <c r="Q4" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.22</v>
-      </c>
       <c r="X4" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>190</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO4" t="n">
         <v>55</v>
       </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="AP4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU4" t="n">
         <v>6.4</v>
       </c>
-      <c r="AC4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD4" t="n">
+      <c r="AV4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD4" t="n">
         <v>27</v>
       </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>42</v>
-      </c>
       <c r="BE4" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1330,186 +1330,186 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Independiente Yumbo</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Boyaca Patriotas</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G5" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H5" t="n">
         <v>3.55</v>
       </c>
       <c r="I5" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="R5" t="n">
         <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X5" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y5" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z5" t="n">
         <v>500</v>
       </c>
-      <c r="Z5" t="n">
-        <v>1000</v>
-      </c>
       <c r="AA5" t="n">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="AB5" t="n">
-        <v>500</v>
+        <v>15.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
         <v>500</v>
       </c>
       <c r="AE5" t="n">
-        <v>270</v>
+        <v>80</v>
       </c>
       <c r="AF5" t="n">
-        <v>75</v>
+        <v>15.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH5" t="n">
         <v>500</v>
       </c>
       <c r="AI5" t="n">
-        <v>380</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AK5" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO5" t="n">
         <v>600</v>
       </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP5" t="n">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="AS5" t="n">
-        <v>44</v>
+        <v>14.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AW5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="BB5" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BC5" t="n">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.1</v>
+        <v>12</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.55</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="J6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K6" t="n">
         <v>3.25</v>
       </c>
-      <c r="K6" t="n">
-        <v>3.45</v>
-      </c>
       <c r="L6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="P6" t="n">
         <v>1.5</v>
       </c>
-      <c r="M6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.72</v>
-      </c>
       <c r="Q6" t="n">
-        <v>2.32</v>
+        <v>2.98</v>
       </c>
       <c r="R6" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="S6" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.92</v>
+        <v>2.42</v>
       </c>
       <c r="U6" t="n">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="W6" t="n">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="X6" t="n">
-        <v>14.5</v>
+        <v>7.6</v>
       </c>
       <c r="Y6" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>190</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>100</v>
+      </c>
+      <c r="BB6" t="n">
         <v>21</v>
       </c>
-      <c r="Z6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>170</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS6" t="n">
+      <c r="BC6" t="n">
         <v>27</v>
       </c>
-      <c r="AT6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BD6" t="n">
-        <v>11.5</v>
+        <v>60</v>
       </c>
       <c r="BE6" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="BF6" t="n">
-        <v>9.6</v>
+        <v>26</v>
       </c>
       <c r="BG6" t="n">
-        <v>11.5</v>
+        <v>46</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,373 +1718,179 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>Quindio</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Orsomarso</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="G7" t="n">
-        <v>2.06</v>
+        <v>1.74</v>
       </c>
       <c r="H7" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="I7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S7" t="n">
         <v>5.3</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="M7" t="n">
+      <c r="T7" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.15</v>
       </c>
-      <c r="N7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.23</v>
-      </c>
       <c r="W7" t="n">
-        <v>1.94</v>
+        <v>2.34</v>
       </c>
       <c r="X7" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
         <v>6.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="AE7" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AI7" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AK7" t="n">
         <v>32</v>
       </c>
       <c r="AL7" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AM7" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="AO7" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV7" t="n">
         <v>11</v>
       </c>
-      <c r="AR7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV7" t="n">
+      <c r="AW7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC7" t="n">
         <v>20</v>
       </c>
-      <c r="AW7" t="n">
-        <v>85</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>26</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>27</v>
-      </c>
       <c r="BD7" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="BE7" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="BF7" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="BG7" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Colombian Primera B</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Quindio</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Orsomarso</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="H8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I8" t="n">
-        <v>8</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="X8" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>48</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH7"/>
+  <dimension ref="A1:BH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -743,184 +743,184 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>Internacional de Palmira</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Real Santander</t>
+          <t>Tigres FC Zipaquira</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.51</v>
+        <v>1.14</v>
       </c>
       <c r="G2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H2" t="n">
+        <v>75</v>
+      </c>
+      <c r="I2" t="n">
+        <v>85</v>
+      </c>
+      <c r="J2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O2" t="n">
         <v>1.55</v>
       </c>
-      <c r="H2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="I2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.35</v>
-      </c>
       <c r="P2" t="n">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.04</v>
+        <v>3.35</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="S2" t="n">
-        <v>3.8</v>
+        <v>12</v>
       </c>
       <c r="T2" t="n">
-        <v>2.12</v>
+        <v>2.96</v>
       </c>
       <c r="U2" t="n">
-        <v>1.78</v>
+        <v>1.26</v>
       </c>
       <c r="V2" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>2.8</v>
+        <v>7.2</v>
       </c>
       <c r="X2" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.2</v>
+        <v>2.78</v>
       </c>
       <c r="AC2" t="n">
         <v>10</v>
       </c>
       <c r="AD2" t="n">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>80</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD2" t="n">
         <v>160</v>
       </c>
-      <c r="AF2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>240</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>170</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>24</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>100</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>40</v>
-      </c>
       <c r="BE2" t="n">
-        <v>150</v>
+        <v>34</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="BG2" t="n">
-        <v>140</v>
+        <v>48</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Internacional de Palmira</t>
+          <t>Independiente Yumbo</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Boyaca Patriotas</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="G3" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.92</v>
+        <v>7.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.49</v>
+        <v>1.15</v>
       </c>
       <c r="P3" t="n">
-        <v>1.62</v>
+        <v>3.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.48</v>
+        <v>1.08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>2.96</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="U3" t="n">
-        <v>1.72</v>
+        <v>3.05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="X3" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.6</v>
+        <v>900</v>
       </c>
       <c r="AD3" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>10.5</v>
+        <v>990</v>
       </c>
       <c r="AH3" t="n">
-        <v>29</v>
+        <v>990</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>38</v>
+        <v>11.5</v>
       </c>
       <c r="AS3" t="n">
         <v>11.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1136,186 +1136,186 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Independiente Yumbo</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Boyaca Patriotas</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="G4" t="n">
-        <v>2.62</v>
+        <v>3.75</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5</v>
+        <v>2.78</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5</v>
+        <v>2.32</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>2.22</v>
       </c>
       <c r="O4" t="n">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="P4" t="n">
-        <v>1.74</v>
+        <v>1.37</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.24</v>
+        <v>3.55</v>
       </c>
       <c r="R4" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9</v>
+        <v>2.46</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="W4" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="X4" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AF4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="AG4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>180</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>390</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>160</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR4" t="n">
         <v>12</v>
       </c>
-      <c r="AH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>190</v>
-      </c>
-      <c r="AJ4" t="n">
+      <c r="AS4" t="n">
         <v>36</v>
       </c>
-      <c r="AK4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO4" t="n">
+      <c r="AT4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>28</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>90</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>60</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>60</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>270</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>110</v>
+      </c>
+      <c r="BG4" t="n">
         <v>55</v>
       </c>
-      <c r="AP4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="G5" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="H5" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="I5" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="L5" t="n">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="N5" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.43</v>
+        <v>1.69</v>
       </c>
       <c r="P5" t="n">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.28</v>
+        <v>3.15</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="S5" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.93</v>
+        <v>2.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="V5" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="W5" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="X5" t="n">
-        <v>14.5</v>
+        <v>7.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AA5" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AB5" t="n">
-        <v>15.5</v>
+        <v>5.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>14</v>
+        <v>7.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AE5" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL5" t="n">
         <v>80</v>
       </c>
-      <c r="AF5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>500</v>
-      </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AN5" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AO5" t="n">
-        <v>600</v>
+        <v>190</v>
       </c>
       <c r="AP5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>10</v>
-      </c>
       <c r="AR5" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AS5" t="n">
-        <v>14.5</v>
+        <v>42</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>9</v>
+        <v>19.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>19.5</v>
+        <v>65</v>
       </c>
       <c r="AX5" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="BA5" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="BB5" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="BC5" t="n">
-        <v>15.5</v>
+        <v>27</v>
       </c>
       <c r="BD5" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.6</v>
+        <v>80</v>
       </c>
       <c r="BF5" t="n">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="BG5" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,373 +1524,179 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>Quindio</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Orsomarso</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="G6" t="n">
-        <v>2.08</v>
+        <v>1.71</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.64</v>
       </c>
-      <c r="M6" t="n">
+      <c r="V6" t="n">
         <v>1.15</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.23</v>
-      </c>
       <c r="W6" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="X6" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="Y6" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
         <v>6.2</v>
       </c>
       <c r="AC6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF6" t="n">
         <v>7.6</v>
       </c>
-      <c r="AD6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>280</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>190</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ6" t="n">
+      <c r="BG6" t="n">
         <v>11</v>
       </c>
-      <c r="AR6" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>85</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>26</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>100</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>60</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>60</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>26</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>46</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Colombian Primera B</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Quindio</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Orsomarso</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="H7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="X7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BH3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,36 +743,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Internacional de Palmira</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="G2" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="H2" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="I2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K2" t="n">
         <v>85</v>
-      </c>
-      <c r="J2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="K2" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -781,34 +781,34 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.35</v>
+        <v>2.08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T2" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="U2" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>7.2</v>
+        <v>50</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -823,104 +823,104 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.78</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>3.7</v>
+        <v>1.86</v>
       </c>
       <c r="AG2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>290</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>42</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE2" t="n">
         <v>14</v>
       </c>
-      <c r="AH2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>80</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>38</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>160</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>34</v>
-      </c>
       <c r="BF2" t="n">
-        <v>28</v>
+        <v>18.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -937,36 +937,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Independiente Yumbo</t>
+          <t>Quindio</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Boyaca Patriotas</t>
+          <t>Orsomarso</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.66</v>
+        <v>9.4</v>
       </c>
       <c r="G3" t="n">
-        <v>1.71</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>6.2</v>
+        <v>1.73</v>
       </c>
       <c r="I3" t="n">
-        <v>6.8</v>
+        <v>1.77</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -975,34 +975,34 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="S3" t="n">
-        <v>2.96</v>
+        <v>1.74</v>
       </c>
       <c r="T3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.17</v>
+        <v>2.34</v>
       </c>
       <c r="W3" t="n">
-        <v>2.42</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1020,25 +1020,25 @@
         <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>2.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AF3" t="n">
         <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>990</v>
+        <v>3.4</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AJ3" t="n">
         <v>1000</v>
@@ -1047,656 +1047,74 @@
         <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD3" t="n">
         <v>11.5</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>75</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Paraguayan Primera Division</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Deportivo Recoleta</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Rubio Nu</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>180</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>390</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>160</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>28</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>90</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>60</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>60</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>100</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>270</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>110</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>55</v>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>2026-03-26 20:30:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Argentinian Primera Division</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Argentinos Juniors</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Lanus</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="X5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>980</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>190</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>27</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>80</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>30</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>46</v>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>2026-03-26 20:30:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Colombian Primera B</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Quindio</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Orsomarso</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="H6" t="n">
-        <v>7</v>
-      </c>
-      <c r="I6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>48</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>48</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
